--- a/trainingwork0/output/problem1_predictions.xlsx
+++ b/trainingwork0/output/problem1_predictions.xlsx
@@ -471,19 +471,19 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>0.3177</v>
+        <v>0.3231</v>
       </c>
       <c r="D2">
-        <v>0.3634</v>
+        <v>0.4036</v>
       </c>
       <c r="E2">
-        <v>0.2773999869823456</v>
+        <v>0.2678999900817871</v>
       </c>
       <c r="F2">
         <v>0.5236</v>
       </c>
       <c r="G2">
-        <v>0.3487</v>
+        <v>0.3707</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -494,19 +494,19 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>0.3174</v>
+        <v>0.322</v>
       </c>
       <c r="D3">
-        <v>0.3599</v>
+        <v>0.4001</v>
       </c>
       <c r="E3">
-        <v>0.2739999890327454</v>
+        <v>0.262800008058548</v>
       </c>
       <c r="F3">
         <v>0.527</v>
       </c>
       <c r="G3">
-        <v>0.3466</v>
+        <v>0.3681</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -517,19 +517,19 @@
         <v>12</v>
       </c>
       <c r="C4">
-        <v>0.3185</v>
+        <v>0.3238</v>
       </c>
       <c r="D4">
-        <v>0.3599</v>
+        <v>0.4001</v>
       </c>
       <c r="E4">
-        <v>0.2739999890327454</v>
+        <v>0.262800008058548</v>
       </c>
       <c r="F4">
         <v>0.5364</v>
       </c>
       <c r="G4">
-        <v>0.3478</v>
+        <v>0.3695</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -540,19 +540,19 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>0.3484</v>
+        <v>0.3508</v>
       </c>
       <c r="D5">
-        <v>0.4044</v>
+        <v>0.4414</v>
       </c>
       <c r="E5">
-        <v>0.3463000059127808</v>
+        <v>0.3407999873161316</v>
       </c>
       <c r="F5">
         <v>0.5286</v>
       </c>
       <c r="G5">
-        <v>0.3909</v>
+        <v>0.4104</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -563,19 +563,19 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>0.3421</v>
+        <v>0.3457</v>
       </c>
       <c r="D6">
-        <v>0.4115</v>
+        <v>0.4448</v>
       </c>
       <c r="E6">
-        <v>0.3508999943733215</v>
+        <v>0.3449999988079071</v>
       </c>
       <c r="F6">
         <v>0.5376</v>
       </c>
       <c r="G6">
-        <v>0.3942</v>
+        <v>0.4123</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -586,19 +586,19 @@
         <v>15</v>
       </c>
       <c r="C7">
-        <v>0.2946</v>
+        <v>0.2908</v>
       </c>
       <c r="D7">
-        <v>0.3894</v>
+        <v>0.4281</v>
       </c>
       <c r="E7">
-        <v>0.3901999890804291</v>
+        <v>0.363099992275238</v>
       </c>
       <c r="F7">
         <v>0.4934</v>
       </c>
       <c r="G7">
-        <v>0.3742</v>
+        <v>0.3873</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -609,19 +609,19 @@
         <v>16</v>
       </c>
       <c r="C8">
-        <v>0.3503</v>
+        <v>0.3512</v>
       </c>
       <c r="D8">
-        <v>0.4061</v>
+        <v>0.4423</v>
       </c>
       <c r="E8">
-        <v>0.3567000031471252</v>
+        <v>0.3528000116348267</v>
       </c>
       <c r="F8">
         <v>0.5528999999999999</v>
       </c>
       <c r="G8">
-        <v>0.3966</v>
+        <v>0.4154</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -632,19 +632,19 @@
         <v>17</v>
       </c>
       <c r="C9">
-        <v>0.3392</v>
+        <v>0.3412</v>
       </c>
       <c r="D9">
-        <v>0.4072</v>
+        <v>0.447</v>
       </c>
       <c r="E9">
-        <v>0.3716000020503998</v>
+        <v>0.3610999882221222</v>
       </c>
       <c r="F9">
         <v>0.5259</v>
       </c>
       <c r="G9">
-        <v>0.3944</v>
+        <v>0.4137</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -655,19 +655,19 @@
         <v>18</v>
       </c>
       <c r="C10">
-        <v>0.3152</v>
+        <v>0.3178</v>
       </c>
       <c r="D10">
-        <v>0.3661</v>
+        <v>0.4068</v>
       </c>
       <c r="E10">
-        <v>0.2831000089645386</v>
+        <v>0.2709999978542328</v>
       </c>
       <c r="F10">
         <v>0.5597</v>
       </c>
       <c r="G10">
-        <v>0.3538</v>
+        <v>0.3747</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -678,19 +678,19 @@
         <v>19</v>
       </c>
       <c r="C11">
-        <v>0.3149</v>
+        <v>0.3183</v>
       </c>
       <c r="D11">
-        <v>0.3495</v>
+        <v>0.3905</v>
       </c>
       <c r="E11">
-        <v>0.2800000011920929</v>
+        <v>0.2712999880313873</v>
       </c>
       <c r="F11">
         <v>0.5547</v>
       </c>
       <c r="G11">
-        <v>0.3448</v>
+        <v>0.3664</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -701,19 +701,19 @@
         <v>20</v>
       </c>
       <c r="C12">
-        <v>0.3172</v>
+        <v>0.3229</v>
       </c>
       <c r="D12">
-        <v>0.3618</v>
+        <v>0.4071</v>
       </c>
       <c r="E12">
-        <v>0.2754999995231628</v>
+        <v>0.2639000117778778</v>
       </c>
       <c r="F12">
         <v>0.5742</v>
       </c>
       <c r="G12">
-        <v>0.3522</v>
+        <v>0.3765</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -724,19 +724,19 @@
         <v>21</v>
       </c>
       <c r="C13">
-        <v>0.3182</v>
+        <v>0.3237</v>
       </c>
       <c r="D13">
-        <v>0.3692</v>
+        <v>0.4141</v>
       </c>
       <c r="E13">
-        <v>0.2745999991893768</v>
+        <v>0.2628999948501587</v>
       </c>
       <c r="F13">
         <v>0.5397999999999999</v>
       </c>
       <c r="G13">
-        <v>0.3525</v>
+        <v>0.3767</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -747,19 +747,19 @@
         <v>10</v>
       </c>
       <c r="C14">
-        <v>0.3159</v>
+        <v>0.3198</v>
       </c>
       <c r="D14">
-        <v>0.3164</v>
+        <v>0.3614</v>
       </c>
       <c r="E14">
-        <v>0.2696999907493591</v>
+        <v>0.2709999978542328</v>
       </c>
       <c r="F14">
         <v>0.5009</v>
       </c>
       <c r="G14">
-        <v>0.3224</v>
+        <v>0.3473</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -770,19 +770,19 @@
         <v>11</v>
       </c>
       <c r="C15">
-        <v>0.3333</v>
+        <v>0.3389</v>
       </c>
       <c r="D15">
-        <v>0.3606</v>
+        <v>0.4068</v>
       </c>
       <c r="E15">
-        <v>0.3517999947071075</v>
+        <v>0.3472000062465668</v>
       </c>
       <c r="F15">
         <v>0.5026</v>
       </c>
       <c r="G15">
-        <v>0.3647</v>
+        <v>0.3885</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -793,19 +793,19 @@
         <v>12</v>
       </c>
       <c r="C16">
-        <v>0.3334</v>
+        <v>0.3389</v>
       </c>
       <c r="D16">
-        <v>0.3821</v>
+        <v>0.4271</v>
       </c>
       <c r="E16">
-        <v>0.362500011920929</v>
+        <v>0.3567000031471252</v>
       </c>
       <c r="F16">
         <v>0.5349</v>
       </c>
       <c r="G16">
-        <v>0.3801</v>
+        <v>0.4033</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -816,19 +816,19 @@
         <v>13</v>
       </c>
       <c r="C17">
-        <v>0.3454</v>
+        <v>0.3462</v>
       </c>
       <c r="D17">
-        <v>0.3789</v>
+        <v>0.4202</v>
       </c>
       <c r="E17">
-        <v>0.3596000075340271</v>
+        <v>0.3519000113010406</v>
       </c>
       <c r="F17">
         <v>0.5354</v>
       </c>
       <c r="G17">
-        <v>0.3814</v>
+        <v>0.4012</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -839,19 +839,19 @@
         <v>14</v>
       </c>
       <c r="C18">
-        <v>0.3451</v>
+        <v>0.3455</v>
       </c>
       <c r="D18">
-        <v>0.3772</v>
+        <v>0.4213</v>
       </c>
       <c r="E18">
-        <v>0.3562999963760376</v>
+        <v>0.3486000001430511</v>
       </c>
       <c r="F18">
         <v>0.5124</v>
       </c>
       <c r="G18">
-        <v>0.3776</v>
+        <v>0.3987</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -862,19 +862,19 @@
         <v>15</v>
       </c>
       <c r="C19">
-        <v>0.3145</v>
+        <v>0.3208</v>
       </c>
       <c r="D19">
-        <v>0.3554</v>
+        <v>0.4065</v>
       </c>
       <c r="E19">
-        <v>0.2702000141143799</v>
+        <v>0.2621999979019165</v>
       </c>
       <c r="F19">
         <v>0.5671</v>
       </c>
       <c r="G19">
-        <v>0.3467</v>
+        <v>0.3746</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -885,19 +885,19 @@
         <v>16</v>
       </c>
       <c r="C20">
-        <v>0.3142</v>
+        <v>0.3197</v>
       </c>
       <c r="D20">
-        <v>0.381</v>
+        <v>0.4292</v>
       </c>
       <c r="E20">
-        <v>0.2766000032424927</v>
+        <v>0.2707000076770782</v>
       </c>
       <c r="F20">
         <v>0.5319</v>
       </c>
       <c r="G20">
-        <v>0.3566</v>
+        <v>0.3836</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -908,19 +908,19 @@
         <v>17</v>
       </c>
       <c r="C21">
-        <v>0.3053</v>
+        <v>0.316</v>
       </c>
       <c r="D21">
-        <v>0.2904</v>
+        <v>0.3153</v>
       </c>
       <c r="E21">
-        <v>0.2806999981403351</v>
+        <v>0.2869000136852264</v>
       </c>
       <c r="F21">
         <v>0.3674</v>
       </c>
       <c r="G21">
-        <v>0.2967</v>
+        <v>0.3134</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -931,19 +931,19 @@
         <v>18</v>
       </c>
       <c r="C22">
-        <v>0.3178</v>
+        <v>0.321</v>
       </c>
       <c r="D22">
-        <v>0.2976</v>
+        <v>0.3225</v>
       </c>
       <c r="E22">
-        <v>0.2797000110149384</v>
+        <v>0.2827000021934509</v>
       </c>
       <c r="F22">
         <v>0.5278</v>
       </c>
       <c r="G22">
-        <v>0.3186</v>
+        <v>0.3329</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -954,19 +954,19 @@
         <v>19</v>
       </c>
       <c r="C23">
-        <v>0.3167</v>
+        <v>0.3215</v>
       </c>
       <c r="D23">
-        <v>0.2971</v>
+        <v>0.3221</v>
       </c>
       <c r="E23">
-        <v>0.2795999944210052</v>
+        <v>0.2824999988079071</v>
       </c>
       <c r="F23">
         <v>0.5214</v>
       </c>
       <c r="G23">
-        <v>0.3175</v>
+        <v>0.3322</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -977,19 +977,19 @@
         <v>20</v>
       </c>
       <c r="C24">
-        <v>0.3162</v>
+        <v>0.3205</v>
       </c>
       <c r="D24">
-        <v>0.2942</v>
+        <v>0.322</v>
       </c>
       <c r="E24">
-        <v>0.2788000106811523</v>
+        <v>0.2825999855995178</v>
       </c>
       <c r="F24">
         <v>0.5115</v>
       </c>
       <c r="G24">
-        <v>0.3148</v>
+        <v>0.331</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1000,19 +1000,19 @@
         <v>21</v>
       </c>
       <c r="C25">
-        <v>0.316</v>
+        <v>0.3208</v>
       </c>
       <c r="D25">
-        <v>0.2903</v>
+        <v>0.3148</v>
       </c>
       <c r="E25">
-        <v>0.2777999937534332</v>
+        <v>0.2806000113487244</v>
       </c>
       <c r="F25">
         <v>0.5188</v>
       </c>
       <c r="G25">
-        <v>0.3134</v>
+        <v>0.3278</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1023,19 +1023,19 @@
         <v>10</v>
       </c>
       <c r="C26">
-        <v>0.1905</v>
+        <v>0.194</v>
       </c>
       <c r="D26">
-        <v>0.311</v>
+        <v>0.3443</v>
       </c>
       <c r="E26">
-        <v>0.2633000016212463</v>
+        <v>0.257999986410141</v>
       </c>
       <c r="F26">
         <v>0.4379</v>
       </c>
       <c r="G26">
-        <v>0.2772</v>
+        <v>0.2948</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1046,19 +1046,19 @@
         <v>11</v>
       </c>
       <c r="C27">
-        <v>0.2348</v>
+        <v>0.2363</v>
       </c>
       <c r="D27">
-        <v>0.3241</v>
+        <v>0.3637</v>
       </c>
       <c r="E27">
-        <v>0.2976999878883362</v>
+        <v>0.2587999999523163</v>
       </c>
       <c r="F27">
         <v>0.3013</v>
       </c>
       <c r="G27">
-        <v>0.2899</v>
+        <v>0.3036</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1069,19 +1069,19 @@
         <v>12</v>
       </c>
       <c r="C28">
-        <v>0.2362</v>
+        <v>0.2374</v>
       </c>
       <c r="D28">
-        <v>0.3109</v>
+        <v>0.3503</v>
       </c>
       <c r="E28">
-        <v>0.3301999866962433</v>
+        <v>0.289900004863739</v>
       </c>
       <c r="F28">
         <v>0.2823</v>
       </c>
       <c r="G28">
-        <v>0.2887</v>
+        <v>0.3008</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1092,19 +1092,19 @@
         <v>13</v>
       </c>
       <c r="C29">
-        <v>0.3512</v>
+        <v>0.3496</v>
       </c>
       <c r="D29">
-        <v>0.4137</v>
+        <v>0.4535</v>
       </c>
       <c r="E29">
-        <v>0.3337000012397766</v>
+        <v>0.3253999948501587</v>
       </c>
       <c r="F29">
         <v>0.5639</v>
       </c>
       <c r="G29">
-        <v>0.3969</v>
+        <v>0.4167</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1115,19 +1115,19 @@
         <v>14</v>
       </c>
       <c r="C30">
-        <v>0.206</v>
+        <v>0.2035</v>
       </c>
       <c r="D30">
-        <v>0.3392</v>
+        <v>0.3678</v>
       </c>
       <c r="E30">
-        <v>0.2651999890804291</v>
+        <v>0.2538000047206879</v>
       </c>
       <c r="F30">
         <v>0.4272</v>
       </c>
       <c r="G30">
-        <v>0.2942</v>
+        <v>0.3074</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1138,19 +1138,19 @@
         <v>15</v>
       </c>
       <c r="C31">
-        <v>0.1968</v>
+        <v>0.1958</v>
       </c>
       <c r="D31">
-        <v>0.3131</v>
+        <v>0.3432</v>
       </c>
       <c r="E31">
-        <v>0.2973999977111816</v>
+        <v>0.2883999943733215</v>
       </c>
       <c r="F31">
         <v>0.4336</v>
       </c>
       <c r="G31">
-        <v>0.2864</v>
+        <v>0.2996</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1161,19 +1161,19 @@
         <v>16</v>
       </c>
       <c r="C32">
-        <v>0.2295</v>
+        <v>0.226</v>
       </c>
       <c r="D32">
-        <v>0.3162</v>
+        <v>0.3638</v>
       </c>
       <c r="E32">
-        <v>0.3228999972343445</v>
+        <v>0.2775999903678894</v>
       </c>
       <c r="F32">
         <v>0.1931</v>
       </c>
       <c r="G32">
-        <v>0.2794</v>
+        <v>0.2936</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1184,19 +1184,19 @@
         <v>17</v>
       </c>
       <c r="C33">
-        <v>0.34</v>
+        <v>0.3389</v>
       </c>
       <c r="D33">
-        <v>0.2922</v>
+        <v>0.3153</v>
       </c>
       <c r="E33">
-        <v>0.3476999998092651</v>
+        <v>0.352400004863739</v>
       </c>
       <c r="F33">
         <v>0.5365</v>
       </c>
       <c r="G33">
-        <v>0.3368</v>
+        <v>0.3474</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1207,19 +1207,19 @@
         <v>18</v>
       </c>
       <c r="C34">
-        <v>0.3404</v>
+        <v>0.3416</v>
       </c>
       <c r="D34">
-        <v>0.3259</v>
+        <v>0.3625</v>
       </c>
       <c r="E34">
-        <v>0.3449999988079071</v>
+        <v>0.3472999930381775</v>
       </c>
       <c r="F34">
         <v>0.5362</v>
       </c>
       <c r="G34">
-        <v>0.3522</v>
+        <v>0.3706</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1230,19 +1230,19 @@
         <v>19</v>
       </c>
       <c r="C35">
-        <v>0.3394</v>
+        <v>0.3415</v>
       </c>
       <c r="D35">
-        <v>0.347</v>
+        <v>0.3942</v>
       </c>
       <c r="E35">
-        <v>0.369700014591217</v>
+        <v>0.3558000028133392</v>
       </c>
       <c r="F35">
         <v>0.527</v>
       </c>
       <c r="G35">
-        <v>0.3659</v>
+        <v>0.3869</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1253,19 +1253,19 @@
         <v>20</v>
       </c>
       <c r="C36">
-        <v>0.3407</v>
+        <v>0.3412</v>
       </c>
       <c r="D36">
-        <v>0.3328</v>
+        <v>0.3798</v>
       </c>
       <c r="E36">
-        <v>0.3600000143051147</v>
+        <v>0.3456999957561493</v>
       </c>
       <c r="F36">
         <v>0.5379</v>
       </c>
       <c r="G36">
-        <v>0.3587</v>
+        <v>0.3789</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1276,10 +1276,10 @@
         <v>21</v>
       </c>
       <c r="C37">
-        <v>0.34</v>
+        <v>0.342</v>
       </c>
       <c r="D37">
-        <v>0.3354</v>
+        <v>0.3827</v>
       </c>
       <c r="E37">
         <v>0.3458999991416931</v>
@@ -1288,7 +1288,7 @@
         <v>0.5092</v>
       </c>
       <c r="G37">
-        <v>0.3542</v>
+        <v>0.3779</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1299,19 +1299,19 @@
         <v>10</v>
       </c>
       <c r="C38">
-        <v>0.2267</v>
+        <v>0.2292</v>
       </c>
       <c r="D38">
-        <v>0.1677</v>
+        <v>0.1658</v>
       </c>
       <c r="E38">
-        <v>0.261000007390976</v>
+        <v>0.2409999966621399</v>
       </c>
       <c r="F38">
         <v>0.2343</v>
       </c>
       <c r="G38">
-        <v>0.2003</v>
+        <v>0.1942</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1322,19 +1322,19 @@
         <v>11</v>
       </c>
       <c r="C39">
-        <v>0.221</v>
+        <v>0.2232</v>
       </c>
       <c r="D39">
-        <v>0.2015</v>
+        <v>0.1996</v>
       </c>
       <c r="E39">
-        <v>0.2585999965667725</v>
+        <v>0.2387000024318695</v>
       </c>
       <c r="F39">
         <v>0.2495</v>
       </c>
       <c r="G39">
-        <v>0.2155</v>
+        <v>0.2102</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1345,19 +1345,19 @@
         <v>12</v>
       </c>
       <c r="C40">
-        <v>0.2085</v>
+        <v>0.2118</v>
       </c>
       <c r="D40">
-        <v>0.2476</v>
+        <v>0.2453</v>
       </c>
       <c r="E40">
-        <v>0.2423000037670135</v>
+        <v>0.2223999947309494</v>
       </c>
       <c r="F40">
         <v>0.228</v>
       </c>
       <c r="G40">
-        <v>0.2284</v>
+        <v>0.2247</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1368,19 +1368,19 @@
         <v>13</v>
       </c>
       <c r="C41">
-        <v>0.4535</v>
+        <v>0.4542</v>
       </c>
       <c r="D41">
-        <v>0.4262</v>
+        <v>0.4186</v>
       </c>
       <c r="E41">
-        <v>0.5094000101089478</v>
+        <v>0.5101000070571899</v>
       </c>
       <c r="F41">
         <v>0.4063</v>
       </c>
       <c r="G41">
-        <v>0.4519</v>
+        <v>0.4462</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1391,19 +1391,19 @@
         <v>14</v>
       </c>
       <c r="C42">
-        <v>0.5165</v>
+        <v>0.5065</v>
       </c>
       <c r="D42">
-        <v>0.4173</v>
+        <v>0.3997</v>
       </c>
       <c r="E42">
-        <v>0.5652999877929688</v>
+        <v>0.5654000043869019</v>
       </c>
       <c r="F42">
         <v>0.5457</v>
       </c>
       <c r="G42">
-        <v>0.4899</v>
+        <v>0.4746</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1414,19 +1414,19 @@
         <v>15</v>
       </c>
       <c r="C43">
-        <v>0.496</v>
+        <v>0.4886</v>
       </c>
       <c r="D43">
-        <v>0.451</v>
+        <v>0.44</v>
       </c>
       <c r="E43">
-        <v>0.6021999716758728</v>
+        <v>0.5938000082969666</v>
       </c>
       <c r="F43">
         <v>0.4648</v>
       </c>
       <c r="G43">
-        <v>0.4997</v>
+        <v>0.4866</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1437,19 +1437,19 @@
         <v>16</v>
       </c>
       <c r="C44">
-        <v>0.4806</v>
+        <v>0.4729</v>
       </c>
       <c r="D44">
-        <v>0.3836</v>
+        <v>0.3846</v>
       </c>
       <c r="E44">
-        <v>0.5837000012397766</v>
+        <v>0.5853999853134155</v>
       </c>
       <c r="F44">
         <v>0.4187</v>
       </c>
       <c r="G44">
-        <v>0.4556</v>
+        <v>0.4489</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1460,19 +1460,19 @@
         <v>17</v>
       </c>
       <c r="C45">
-        <v>0.494</v>
+        <v>0.485</v>
       </c>
       <c r="D45">
-        <v>0.3455</v>
+        <v>0.3432</v>
       </c>
       <c r="E45">
-        <v>0.5870000123977661</v>
+        <v>0.5885000228881836</v>
       </c>
       <c r="F45">
         <v>0.4365</v>
       </c>
       <c r="G45">
-        <v>0.4438</v>
+        <v>0.4342</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1483,19 +1483,19 @@
         <v>18</v>
       </c>
       <c r="C46">
-        <v>0.2334</v>
+        <v>0.2369</v>
       </c>
       <c r="D46">
-        <v>0.1914</v>
+        <v>0.1881</v>
       </c>
       <c r="E46">
-        <v>0.2599000036716461</v>
+        <v>0.2381999939680099</v>
       </c>
       <c r="F46">
         <v>0.325</v>
       </c>
       <c r="G46">
-        <v>0.2217</v>
+        <v>0.2155</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1506,19 +1506,19 @@
         <v>19</v>
       </c>
       <c r="C47">
-        <v>0.2292</v>
+        <v>0.2303</v>
       </c>
       <c r="D47">
-        <v>0.2062</v>
+        <v>0.205</v>
       </c>
       <c r="E47">
-        <v>0.256199985742569</v>
+        <v>0.2339999973773956</v>
       </c>
       <c r="F47">
         <v>0.3007</v>
       </c>
       <c r="G47">
-        <v>0.2245</v>
+        <v>0.219</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1529,19 +1529,19 @@
         <v>20</v>
       </c>
       <c r="C48">
-        <v>0.2296</v>
+        <v>0.2323</v>
       </c>
       <c r="D48">
-        <v>0.1782</v>
+        <v>0.177</v>
       </c>
       <c r="E48">
-        <v>0.2551000118255615</v>
+        <v>0.2346999943256378</v>
       </c>
       <c r="F48">
         <v>0.1852</v>
       </c>
       <c r="G48">
-        <v>0.2002</v>
+        <v>0.1948</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1552,19 +1552,19 @@
         <v>21</v>
       </c>
       <c r="C49">
-        <v>0.2298</v>
+        <v>0.2308</v>
       </c>
       <c r="D49">
-        <v>0.1784</v>
+        <v>0.1765</v>
       </c>
       <c r="E49">
-        <v>0.2502000033855438</v>
+        <v>0.2301999926567078</v>
       </c>
       <c r="F49">
         <v>0.1537</v>
       </c>
       <c r="G49">
-        <v>0.1964</v>
+        <v>0.1903</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1575,19 +1575,19 @@
         <v>10</v>
       </c>
       <c r="C50">
-        <v>0.2108</v>
+        <v>0.2106</v>
       </c>
       <c r="D50">
-        <v>0.2949</v>
+        <v>0.2918</v>
       </c>
       <c r="E50">
-        <v>0.2509999871253967</v>
+        <v>0.2310000061988831</v>
       </c>
       <c r="F50">
         <v>0.1738</v>
       </c>
       <c r="G50">
-        <v>0.2479</v>
+        <v>0.2437</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1598,19 +1598,19 @@
         <v>11</v>
       </c>
       <c r="C51">
-        <v>0.2107</v>
+        <v>0.2112</v>
       </c>
       <c r="D51">
-        <v>0.5454</v>
+        <v>0.5283</v>
       </c>
       <c r="E51">
-        <v>0.2777999937534332</v>
+        <v>0.2626000046730042</v>
       </c>
       <c r="F51">
         <v>0.1751</v>
       </c>
       <c r="G51">
-        <v>0.3711</v>
+        <v>0.3665</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1621,19 +1621,19 @@
         <v>12</v>
       </c>
       <c r="C52">
-        <v>0.2078</v>
+        <v>0.2088</v>
       </c>
       <c r="D52">
-        <v>0.5305</v>
+        <v>0.5155999999999999</v>
       </c>
       <c r="E52">
-        <v>0.2773999869823456</v>
+        <v>0.2621999979019165</v>
       </c>
       <c r="F52">
         <v>0.1987</v>
       </c>
       <c r="G52">
-        <v>0.3654</v>
+        <v>0.3617</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1644,19 +1644,19 @@
         <v>13</v>
       </c>
       <c r="C53">
-        <v>0.2424</v>
+        <v>0.2419</v>
       </c>
       <c r="D53">
-        <v>0.2222</v>
+        <v>0.2199</v>
       </c>
       <c r="E53">
-        <v>0.2517000138759613</v>
+        <v>0.2317000031471252</v>
       </c>
       <c r="F53">
         <v>0.1623</v>
       </c>
       <c r="G53">
-        <v>0.2216</v>
+        <v>0.216</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1667,19 +1667,19 @@
         <v>14</v>
       </c>
       <c r="C54">
-        <v>0.2074</v>
+        <v>0.2075</v>
       </c>
       <c r="D54">
-        <v>0.2111</v>
+        <v>0.2079</v>
       </c>
       <c r="E54">
-        <v>0.2322999984025955</v>
+        <v>0.2123000025749207</v>
       </c>
       <c r="F54">
         <v>0.1566</v>
       </c>
       <c r="G54">
-        <v>0.2021</v>
+        <v>0.1964</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1693,16 +1693,16 @@
         <v>0.2086</v>
       </c>
       <c r="D55">
-        <v>0.2409</v>
+        <v>0.2378</v>
       </c>
       <c r="E55">
-        <v>0.2339999973773956</v>
+        <v>0.2141000032424927</v>
       </c>
       <c r="F55">
         <v>0.1707</v>
       </c>
       <c r="G55">
-        <v>0.2182</v>
+        <v>0.2132</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1713,19 +1713,19 @@
         <v>16</v>
       </c>
       <c r="C56">
-        <v>0.208</v>
+        <v>0.2077</v>
       </c>
       <c r="D56">
-        <v>0.2346</v>
+        <v>0.2315</v>
       </c>
       <c r="E56">
-        <v>0.2369000017642975</v>
+        <v>0.2169000059366226</v>
       </c>
       <c r="F56">
         <v>0.1809</v>
       </c>
       <c r="G56">
-        <v>0.2166</v>
+        <v>0.2112</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1736,19 +1736,19 @@
         <v>17</v>
       </c>
       <c r="C57">
-        <v>0.2055</v>
+        <v>0.2048</v>
       </c>
       <c r="D57">
-        <v>0.2468</v>
+        <v>0.2427</v>
       </c>
       <c r="E57">
-        <v>0.2430000007152557</v>
+        <v>0.2230000048875809</v>
       </c>
       <c r="F57">
         <v>0.1495</v>
       </c>
       <c r="G57">
-        <v>0.2199</v>
+        <v>0.2141</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1759,19 +1759,19 @@
         <v>18</v>
       </c>
       <c r="C58">
-        <v>0.2053</v>
+        <v>0.2048</v>
       </c>
       <c r="D58">
-        <v>0.2619</v>
+        <v>0.2568</v>
       </c>
       <c r="E58">
-        <v>0.2513000071048737</v>
+        <v>0.2310000061988831</v>
       </c>
       <c r="F58">
         <v>0.1774</v>
       </c>
       <c r="G58">
-        <v>0.2312</v>
+        <v>0.2251</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1782,19 +1782,19 @@
         <v>19</v>
       </c>
       <c r="C59">
-        <v>0.2057</v>
+        <v>0.2059</v>
       </c>
       <c r="D59">
-        <v>0.2413</v>
+        <v>0.243</v>
       </c>
       <c r="E59">
-        <v>0.2545000016689301</v>
+        <v>0.2340999990701675</v>
       </c>
       <c r="F59">
         <v>0.2231</v>
       </c>
       <c r="G59">
-        <v>0.2266</v>
+        <v>0.2234</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1808,16 +1808,16 @@
         <v>0.2071</v>
       </c>
       <c r="D60">
-        <v>0.2304</v>
+        <v>0.2252</v>
       </c>
       <c r="E60">
-        <v>0.246399998664856</v>
+        <v>0.2260999977588654</v>
       </c>
       <c r="F60">
         <v>0.1818</v>
       </c>
       <c r="G60">
-        <v>0.2163</v>
+        <v>0.2096</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1828,19 +1828,19 @@
         <v>21</v>
       </c>
       <c r="C61">
-        <v>0.2043</v>
+        <v>0.2063</v>
       </c>
       <c r="D61">
-        <v>0.2618</v>
+        <v>0.2591</v>
       </c>
       <c r="E61">
-        <v>0.2502000033855438</v>
+        <v>0.2298000007867813</v>
       </c>
       <c r="F61">
         <v>0.218</v>
       </c>
       <c r="G61">
-        <v>0.2345</v>
+        <v>0.2303</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1851,19 +1851,19 @@
         <v>10</v>
       </c>
       <c r="C62">
-        <v>0.2088</v>
+        <v>0.2095</v>
       </c>
       <c r="D62">
-        <v>0.3717</v>
+        <v>0.3715</v>
       </c>
       <c r="E62">
-        <v>0.2869000136852264</v>
+        <v>0.2718000113964081</v>
       </c>
       <c r="F62">
         <v>0.2546</v>
       </c>
       <c r="G62">
-        <v>0.2983</v>
+        <v>0.2976</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1874,19 +1874,19 @@
         <v>11</v>
       </c>
       <c r="C63">
-        <v>0.2061</v>
+        <v>0.2057</v>
       </c>
       <c r="D63">
-        <v>0.5</v>
+        <v>0.4834</v>
       </c>
       <c r="E63">
-        <v>0.2838000059127808</v>
+        <v>0.2687999904155731</v>
       </c>
       <c r="F63">
         <v>0.2369</v>
       </c>
       <c r="G63">
-        <v>0.3556</v>
+        <v>0.3497</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1897,19 +1897,19 @@
         <v>12</v>
       </c>
       <c r="C64">
-        <v>0.2022</v>
+        <v>0.2035</v>
       </c>
       <c r="D64">
-        <v>0.4981</v>
+        <v>0.4838</v>
       </c>
       <c r="E64">
-        <v>0.2858000099658966</v>
+        <v>0.26910001039505</v>
       </c>
       <c r="F64">
         <v>0.268</v>
       </c>
       <c r="G64">
-        <v>0.3569</v>
+        <v>0.3523</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1920,19 +1920,19 @@
         <v>13</v>
       </c>
       <c r="C65">
-        <v>0.1975</v>
+        <v>0.1994</v>
       </c>
       <c r="D65">
-        <v>0.5108</v>
+        <v>0.4942</v>
       </c>
       <c r="E65">
-        <v>0.2790000140666962</v>
+        <v>0.2623000144958496</v>
       </c>
       <c r="F65">
         <v>0.2195</v>
       </c>
       <c r="G65">
-        <v>0.3556</v>
+        <v>0.3504</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1943,19 +1943,19 @@
         <v>14</v>
       </c>
       <c r="C66">
-        <v>0.2058</v>
+        <v>0.2068</v>
       </c>
       <c r="D66">
         <v>0.2348</v>
       </c>
       <c r="E66">
-        <v>0.249099999666214</v>
+        <v>0.2339999973773956</v>
       </c>
       <c r="F66">
         <v>0.2448</v>
       </c>
       <c r="G66">
-        <v>0.2245</v>
+        <v>0.2217</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1966,19 +1966,19 @@
         <v>15</v>
       </c>
       <c r="C67">
-        <v>0.2253</v>
+        <v>0.2264</v>
       </c>
       <c r="D67">
-        <v>0.2624</v>
+        <v>0.2615</v>
       </c>
       <c r="E67">
-        <v>0.2363999933004379</v>
+        <v>0.2213000059127808</v>
       </c>
       <c r="F67">
         <v>0.2956</v>
       </c>
       <c r="G67">
-        <v>0.2453</v>
+        <v>0.2431</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1989,19 +1989,19 @@
         <v>16</v>
       </c>
       <c r="C68">
-        <v>0.2269</v>
+        <v>0.2256</v>
       </c>
       <c r="D68">
         <v>0.2883</v>
       </c>
       <c r="E68">
-        <v>0.24269999563694</v>
+        <v>0.2254000008106232</v>
       </c>
       <c r="F68">
         <v>0.3179</v>
       </c>
       <c r="G68">
-        <v>0.2613</v>
+        <v>0.259</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -2012,19 +2012,19 @@
         <v>17</v>
       </c>
       <c r="C69">
-        <v>0.2312</v>
+        <v>0.2305</v>
       </c>
       <c r="D69">
-        <v>0.3074</v>
+        <v>0.3078</v>
       </c>
       <c r="E69">
-        <v>0.2664999961853027</v>
+        <v>0.2449000030755997</v>
       </c>
       <c r="F69">
         <v>0.3559</v>
       </c>
       <c r="G69">
-        <v>0.2799</v>
+        <v>0.277</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -2035,19 +2035,19 @@
         <v>18</v>
       </c>
       <c r="C70">
-        <v>0.4401</v>
+        <v>0.4309</v>
       </c>
       <c r="D70">
-        <v>0.4819</v>
+        <v>0.5054999999999999</v>
       </c>
       <c r="E70">
-        <v>0.4603999853134155</v>
+        <v>0.4772999882698059</v>
       </c>
       <c r="F70">
         <v>0.5733</v>
       </c>
       <c r="G70">
-        <v>0.4803</v>
+        <v>0.4928</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2058,19 +2058,19 @@
         <v>19</v>
       </c>
       <c r="C71">
-        <v>0.3504</v>
+        <v>0.3568</v>
       </c>
       <c r="D71">
-        <v>0.4008</v>
+        <v>0.3992</v>
       </c>
       <c r="E71">
-        <v>0.3826999962329865</v>
+        <v>0.3912999927997589</v>
       </c>
       <c r="F71">
         <v>0.3856</v>
       </c>
       <c r="G71">
-        <v>0.3835</v>
+        <v>0.3863</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2081,19 +2081,19 @@
         <v>20</v>
       </c>
       <c r="C72">
-        <v>0.4518</v>
+        <v>0.4502</v>
       </c>
       <c r="D72">
-        <v>0.4605</v>
+        <v>0.4532</v>
       </c>
       <c r="E72">
-        <v>0.4763999879360199</v>
+        <v>0.4749999940395355</v>
       </c>
       <c r="F72">
         <v>0.3615</v>
       </c>
       <c r="G72">
-        <v>0.4567</v>
+        <v>0.4518</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2104,19 +2104,19 @@
         <v>21</v>
       </c>
       <c r="C73">
-        <v>0.4468</v>
+        <v>0.4422</v>
       </c>
       <c r="D73">
-        <v>0.4728</v>
+        <v>0.4671</v>
       </c>
       <c r="E73">
-        <v>0.4715999960899353</v>
+        <v>0.4754000008106232</v>
       </c>
       <c r="F73">
         <v>0.3687</v>
       </c>
       <c r="G73">
-        <v>0.4608</v>
+        <v>0.4572</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2127,13 +2127,13 @@
         <v>10</v>
       </c>
       <c r="C74">
-        <v>0.2245</v>
+        <v>0.225</v>
       </c>
       <c r="D74">
-        <v>0.3889</v>
+        <v>0.3894</v>
       </c>
       <c r="E74">
-        <v>0.257999986410141</v>
+        <v>0.2380000054836273</v>
       </c>
       <c r="F74">
         <v>0.3569</v>
@@ -2150,19 +2150,19 @@
         <v>11</v>
       </c>
       <c r="C75">
-        <v>0.2211</v>
+        <v>0.2199</v>
       </c>
       <c r="D75">
-        <v>0.3191</v>
+        <v>0.3192</v>
       </c>
       <c r="E75">
-        <v>0.2259999960660934</v>
+        <v>0.2060000002384186</v>
       </c>
       <c r="F75">
         <v>0.3347</v>
       </c>
       <c r="G75">
-        <v>0.2724</v>
+        <v>0.2709</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2173,19 +2173,19 @@
         <v>12</v>
       </c>
       <c r="C76">
-        <v>0.2272</v>
+        <v>0.2279</v>
       </c>
       <c r="D76">
-        <v>0.351</v>
+        <v>0.3589</v>
       </c>
       <c r="E76">
-        <v>0.255299985408783</v>
+        <v>0.2322999984025955</v>
       </c>
       <c r="F76">
         <v>0.3677</v>
       </c>
       <c r="G76">
-        <v>0.2981</v>
+        <v>0.3005</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2196,19 +2196,19 @@
         <v>13</v>
       </c>
       <c r="C77">
-        <v>0.5058</v>
+        <v>0.5082</v>
       </c>
       <c r="D77">
-        <v>0.4934</v>
+        <v>0.5024</v>
       </c>
       <c r="E77">
-        <v>0.5454000234603882</v>
+        <v>0.5304999947547913</v>
       </c>
       <c r="F77">
         <v>0.2832</v>
       </c>
       <c r="G77">
-        <v>0.4938</v>
+        <v>0.4948</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2219,19 +2219,19 @@
         <v>14</v>
       </c>
       <c r="C78">
-        <v>0.5084</v>
+        <v>0.5129</v>
       </c>
       <c r="D78">
-        <v>0.5069</v>
+        <v>0.5251</v>
       </c>
       <c r="E78">
-        <v>0.5504999756813049</v>
+        <v>0.5353999733924866</v>
       </c>
       <c r="F78">
         <v>0.2439</v>
       </c>
       <c r="G78">
-        <v>0.4982</v>
+        <v>0.5044</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2242,19 +2242,19 @@
         <v>15</v>
       </c>
       <c r="C79">
-        <v>0.2318</v>
+        <v>0.2345</v>
       </c>
       <c r="D79">
         <v>0.3326</v>
       </c>
       <c r="E79">
-        <v>0.2599999904632568</v>
+        <v>0.2405000030994415</v>
       </c>
       <c r="F79">
         <v>0.3367</v>
       </c>
       <c r="G79">
-        <v>0.2888</v>
+        <v>0.2878</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2265,19 +2265,19 @@
         <v>16</v>
       </c>
       <c r="C80">
-        <v>0.2193</v>
+        <v>0.2197</v>
       </c>
       <c r="D80">
         <v>0.2935</v>
       </c>
       <c r="E80">
-        <v>0.2314999997615814</v>
+        <v>0.2115000039339066</v>
       </c>
       <c r="F80">
         <v>0.2949</v>
       </c>
       <c r="G80">
-        <v>0.2572</v>
+        <v>0.2553</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2288,19 +2288,19 @@
         <v>17</v>
       </c>
       <c r="C81">
-        <v>0.4639</v>
+        <v>0.4561</v>
       </c>
       <c r="D81">
-        <v>0.4233</v>
+        <v>0.4209</v>
       </c>
       <c r="E81">
-        <v>0.4991999864578247</v>
+        <v>0.4842000007629395</v>
       </c>
       <c r="F81">
         <v>0.3482</v>
       </c>
       <c r="G81">
-        <v>0.4459</v>
+        <v>0.4378</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2311,19 +2311,19 @@
         <v>18</v>
       </c>
       <c r="C82">
-        <v>0.4584</v>
+        <v>0.454</v>
       </c>
       <c r="D82">
         <v>0.4278</v>
       </c>
       <c r="E82">
-        <v>0.5146999955177307</v>
+        <v>0.4903999865055084</v>
       </c>
       <c r="F82">
         <v>0.3077</v>
       </c>
       <c r="G82">
-        <v>0.4457</v>
+        <v>0.4379</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2334,19 +2334,19 @@
         <v>19</v>
       </c>
       <c r="C83">
-        <v>0.2211</v>
+        <v>0.223</v>
       </c>
       <c r="D83">
-        <v>0.3543</v>
+        <v>0.3494</v>
       </c>
       <c r="E83">
-        <v>0.2527999877929688</v>
+        <v>0.2298000007867813</v>
       </c>
       <c r="F83">
         <v>0.2909</v>
       </c>
       <c r="G83">
-        <v>0.2902</v>
+        <v>0.2867</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2357,19 +2357,19 @@
         <v>20</v>
       </c>
       <c r="C84">
-        <v>0.2277</v>
+        <v>0.2255</v>
       </c>
       <c r="D84">
-        <v>0.3643</v>
+        <v>0.371</v>
       </c>
       <c r="E84">
-        <v>0.2524999976158142</v>
+        <v>0.2294999957084656</v>
       </c>
       <c r="F84">
         <v>0.2879</v>
       </c>
       <c r="G84">
-        <v>0.2964</v>
+        <v>0.2977</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2380,19 +2380,19 @@
         <v>21</v>
       </c>
       <c r="C85">
-        <v>0.2237</v>
+        <v>0.2251</v>
       </c>
       <c r="D85">
-        <v>0.3564</v>
+        <v>0.3631</v>
       </c>
       <c r="E85">
-        <v>0.2527999877929688</v>
+        <v>0.2298000007867813</v>
       </c>
       <c r="F85">
         <v>0.2906</v>
       </c>
       <c r="G85">
-        <v>0.2919</v>
+        <v>0.294</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2403,19 +2403,19 @@
         <v>10</v>
       </c>
       <c r="C86">
-        <v>0.4375</v>
+        <v>0.435</v>
       </c>
       <c r="D86">
-        <v>0.5617</v>
+        <v>0.5521</v>
       </c>
       <c r="E86">
-        <v>0.501800000667572</v>
+        <v>0.4749999940395355</v>
       </c>
       <c r="F86">
         <v>0.3911</v>
       </c>
       <c r="G86">
-        <v>0.5082</v>
+        <v>0.4992</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2426,19 +2426,19 @@
         <v>11</v>
       </c>
       <c r="C87">
-        <v>0.4434</v>
+        <v>0.4448</v>
       </c>
       <c r="D87">
-        <v>0.5363</v>
+        <v>0.5308</v>
       </c>
       <c r="E87">
-        <v>0.506600022315979</v>
+        <v>0.4790000021457672</v>
       </c>
       <c r="F87">
         <v>0.4074</v>
       </c>
       <c r="G87">
-        <v>0.5004</v>
+        <v>0.4937</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2449,19 +2449,19 @@
         <v>12</v>
       </c>
       <c r="C88">
-        <v>0.4439</v>
+        <v>0.4396</v>
       </c>
       <c r="D88">
-        <v>0.5417</v>
+        <v>0.5362</v>
       </c>
       <c r="E88">
-        <v>0.5023000240325928</v>
+        <v>0.4754000008106232</v>
       </c>
       <c r="F88">
         <v>0.4082</v>
       </c>
       <c r="G88">
-        <v>0.5022</v>
+        <v>0.4944</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2472,19 +2472,19 @@
         <v>13</v>
       </c>
       <c r="C89">
-        <v>0.484</v>
+        <v>0.4754</v>
       </c>
       <c r="D89">
-        <v>0.5321</v>
+        <v>0.525</v>
       </c>
       <c r="E89">
-        <v>0.5394999980926514</v>
+        <v>0.5123000144958496</v>
       </c>
       <c r="F89">
         <v>0.191</v>
       </c>
       <c r="G89">
-        <v>0.4959</v>
+        <v>0.4847</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2495,19 +2495,19 @@
         <v>14</v>
       </c>
       <c r="C90">
-        <v>0.5024</v>
+        <v>0.4944</v>
       </c>
       <c r="D90">
-        <v>0.537</v>
+        <v>0.53</v>
       </c>
       <c r="E90">
-        <v>0.4957999885082245</v>
+        <v>0.4670000076293945</v>
       </c>
       <c r="F90">
         <v>0.1841</v>
       </c>
       <c r="G90">
-        <v>0.4939</v>
+        <v>0.484</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2518,19 +2518,19 @@
         <v>15</v>
       </c>
       <c r="C91">
-        <v>0.5579</v>
+        <v>0.5458</v>
       </c>
       <c r="D91">
-        <v>0.5026</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="E91">
-        <v>0.5636000037193298</v>
+        <v>0.5378999710083008</v>
       </c>
       <c r="F91">
         <v>0.2863</v>
       </c>
       <c r="G91">
-        <v>0.5167</v>
+        <v>0.5061</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2541,19 +2541,19 @@
         <v>16</v>
       </c>
       <c r="C92">
-        <v>0.5081</v>
+        <v>0.4946</v>
       </c>
       <c r="D92">
-        <v>0.4924</v>
+        <v>0.4902</v>
       </c>
       <c r="E92">
-        <v>0.5245000123977661</v>
+        <v>0.5031999945640564</v>
       </c>
       <c r="F92">
         <v>0.3698</v>
       </c>
       <c r="G92">
-        <v>0.498</v>
+        <v>0.4884</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2564,19 +2564,19 @@
         <v>17</v>
       </c>
       <c r="C93">
-        <v>0.5162</v>
+        <v>0.5048</v>
       </c>
       <c r="D93">
-        <v>0.4792</v>
+        <v>0.4769</v>
       </c>
       <c r="E93">
-        <v>0.5332000255584717</v>
+        <v>0.510699987411499</v>
       </c>
       <c r="F93">
         <v>0.3833</v>
       </c>
       <c r="G93">
-        <v>0.4971</v>
+        <v>0.4873</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2587,19 +2587,19 @@
         <v>18</v>
       </c>
       <c r="C94">
-        <v>0.5134</v>
+        <v>0.502</v>
       </c>
       <c r="D94">
-        <v>0.4853</v>
+        <v>0.4831</v>
       </c>
       <c r="E94">
-        <v>0.5295000076293945</v>
+        <v>0.5083000063896179</v>
       </c>
       <c r="F94">
         <v>0.3739</v>
       </c>
       <c r="G94">
-        <v>0.4975</v>
+        <v>0.4883</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2610,19 +2610,19 @@
         <v>19</v>
       </c>
       <c r="C95">
-        <v>0.4678</v>
+        <v>0.4574</v>
       </c>
       <c r="D95">
-        <v>0.674</v>
+        <v>0.66</v>
       </c>
       <c r="E95">
-        <v>0.5220999717712402</v>
+        <v>0.4927000105381012</v>
       </c>
       <c r="F95">
         <v>0.412</v>
       </c>
       <c r="G95">
-        <v>0.5755</v>
+        <v>0.5641</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2633,19 +2633,19 @@
         <v>20</v>
       </c>
       <c r="C96">
-        <v>0.4706</v>
+        <v>0.4628</v>
       </c>
       <c r="D96">
-        <v>0.6761</v>
+        <v>0.6669</v>
       </c>
       <c r="E96">
-        <v>0.5250999927520752</v>
+        <v>0.4936000108718872</v>
       </c>
       <c r="F96">
         <v>0.4493</v>
       </c>
       <c r="G96">
-        <v>0.5814</v>
+        <v>0.5727</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2656,19 +2656,19 @@
         <v>21</v>
       </c>
       <c r="C97">
-        <v>0.4349</v>
+        <v>0.4262</v>
       </c>
       <c r="D97">
-        <v>0.6734</v>
+        <v>0.6569</v>
       </c>
       <c r="E97">
-        <v>0.5145000219345093</v>
+        <v>0.4857999980449677</v>
       </c>
       <c r="F97">
         <v>0.4499</v>
       </c>
       <c r="G97">
-        <v>0.5679999999999999</v>
+        <v>0.5561</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2679,19 +2679,19 @@
         <v>10</v>
       </c>
       <c r="C98">
-        <v>0.4468</v>
+        <v>0.4405</v>
       </c>
       <c r="D98">
-        <v>0.6306</v>
+        <v>0.6272</v>
       </c>
       <c r="E98">
-        <v>0.5034000277519226</v>
+        <v>0.4754999876022339</v>
       </c>
       <c r="F98">
         <v>0.4274</v>
       </c>
       <c r="G98">
-        <v>0.5469000000000001</v>
+        <v>0.5415</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2702,19 +2702,19 @@
         <v>11</v>
       </c>
       <c r="C99">
-        <v>0.4437</v>
+        <v>0.4355</v>
       </c>
       <c r="D99">
-        <v>0.6294999999999999</v>
+        <v>0.6312</v>
       </c>
       <c r="E99">
-        <v>0.4880000054836273</v>
+        <v>0.459199994802475</v>
       </c>
       <c r="F99">
         <v>0.4161</v>
       </c>
       <c r="G99">
-        <v>0.5414</v>
+        <v>0.5382</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2725,19 +2725,19 @@
         <v>12</v>
       </c>
       <c r="C100">
-        <v>0.4649</v>
+        <v>0.4558</v>
       </c>
       <c r="D100">
-        <v>0.6425999999999999</v>
+        <v>0.6446</v>
       </c>
       <c r="E100">
-        <v>0.5514000058174133</v>
+        <v>0.4984999895095825</v>
       </c>
       <c r="F100">
         <v>0.3836</v>
       </c>
       <c r="G100">
-        <v>0.5631</v>
+        <v>0.5543</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2748,19 +2748,19 @@
         <v>13</v>
       </c>
       <c r="C101">
-        <v>0.436</v>
+        <v>0.4189</v>
       </c>
       <c r="D101">
-        <v>0.5867</v>
+        <v>0.5782</v>
       </c>
       <c r="E101">
-        <v>0.4984000027179718</v>
+        <v>0.4607000052928925</v>
       </c>
       <c r="F101">
         <v>0.4107</v>
       </c>
       <c r="G101">
-        <v>0.5207000000000001</v>
+        <v>0.507</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2771,19 +2771,19 @@
         <v>14</v>
       </c>
       <c r="C102">
-        <v>0.4478</v>
+        <v>0.4411</v>
       </c>
       <c r="D102">
-        <v>0.5285</v>
+        <v>0.5185</v>
       </c>
       <c r="E102">
-        <v>0.5223000049591064</v>
+        <v>0.4814999997615814</v>
       </c>
       <c r="F102">
         <v>0.3522</v>
       </c>
       <c r="G102">
-        <v>0.4958</v>
+        <v>0.4818</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -2794,19 +2794,19 @@
         <v>15</v>
       </c>
       <c r="C103">
-        <v>0.3508</v>
+        <v>0.3485</v>
       </c>
       <c r="D103">
-        <v>0.5662</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="E103">
-        <v>0.4013999998569489</v>
+        <v>0.3842000067234039</v>
       </c>
       <c r="F103">
         <v>0.4067</v>
       </c>
       <c r="G103">
-        <v>0.4671</v>
+        <v>0.4654</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -2817,19 +2817,19 @@
         <v>16</v>
       </c>
       <c r="C104">
-        <v>0.3508</v>
+        <v>0.3487</v>
       </c>
       <c r="D104">
-        <v>0.573</v>
+        <v>0.5674</v>
       </c>
       <c r="E104">
-        <v>0.4009000062942505</v>
+        <v>0.3842000067234039</v>
       </c>
       <c r="F104">
         <v>0.4025</v>
       </c>
       <c r="G104">
-        <v>0.4699</v>
+        <v>0.4676</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -2840,19 +2840,19 @@
         <v>17</v>
       </c>
       <c r="C105">
-        <v>0.4326</v>
+        <v>0.435</v>
       </c>
       <c r="D105">
-        <v>0.5041</v>
+        <v>0.504</v>
       </c>
       <c r="E105">
-        <v>0.4866999983787537</v>
+        <v>0.4582000076770782</v>
       </c>
       <c r="F105">
         <v>0.4892</v>
       </c>
       <c r="G105">
-        <v>0.4859</v>
+        <v>0.4819</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -2863,19 +2863,19 @@
         <v>18</v>
       </c>
       <c r="C106">
-        <v>0.46</v>
+        <v>0.4579</v>
       </c>
       <c r="D106">
-        <v>0.4429</v>
+        <v>0.4445</v>
       </c>
       <c r="E106">
-        <v>0.5146999955177307</v>
+        <v>0.4893999993801117</v>
       </c>
       <c r="F106">
         <v>0.4363</v>
       </c>
       <c r="G106">
-        <v>0.4655</v>
+        <v>0.4593</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -2886,19 +2886,19 @@
         <v>19</v>
       </c>
       <c r="C107">
-        <v>0.4532</v>
+        <v>0.4518</v>
       </c>
       <c r="D107">
-        <v>0.449</v>
+        <v>0.4562</v>
       </c>
       <c r="E107">
-        <v>0.5178999900817871</v>
+        <v>0.4932999908924103</v>
       </c>
       <c r="F107">
         <v>0.391</v>
       </c>
       <c r="G107">
-        <v>0.4628</v>
+        <v>0.4597</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -2909,19 +2909,19 @@
         <v>20</v>
       </c>
       <c r="C108">
-        <v>0.4706</v>
+        <v>0.4674</v>
       </c>
       <c r="D108">
-        <v>0.472</v>
+        <v>0.4776</v>
       </c>
       <c r="E108">
-        <v>0.5523999929428101</v>
+        <v>0.5286999940872192</v>
       </c>
       <c r="F108">
         <v>0.3645</v>
       </c>
       <c r="G108">
-        <v>0.4829</v>
+        <v>0.4784</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -2932,19 +2932,19 @@
         <v>21</v>
       </c>
       <c r="C109">
-        <v>0.4371</v>
+        <v>0.4325</v>
       </c>
       <c r="D109">
-        <v>0.6176</v>
+        <v>0.6198</v>
       </c>
       <c r="E109">
-        <v>0.5091000199317932</v>
+        <v>0.4803000092506409</v>
       </c>
       <c r="F109">
         <v>0.3761</v>
       </c>
       <c r="G109">
-        <v>0.5344</v>
+        <v>0.5315</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -2955,19 +2955,19 @@
         <v>10</v>
       </c>
       <c r="C110">
-        <v>0.4317</v>
+        <v>0.4244</v>
       </c>
       <c r="D110">
-        <v>0.5198</v>
+        <v>0.5226</v>
       </c>
       <c r="E110">
-        <v>0.5034999847412109</v>
+        <v>0.4672000110149384</v>
       </c>
       <c r="F110">
         <v>0.2358</v>
       </c>
       <c r="G110">
-        <v>0.4724</v>
+        <v>0.4655</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -2978,19 +2978,19 @@
         <v>11</v>
       </c>
       <c r="C111">
-        <v>0.438</v>
+        <v>0.4267</v>
       </c>
       <c r="D111">
         <v>0.5448</v>
       </c>
       <c r="E111">
-        <v>0.5090000033378601</v>
+        <v>0.4869999885559082</v>
       </c>
       <c r="F111">
         <v>0.3553</v>
       </c>
       <c r="G111">
-        <v>0.4984</v>
+        <v>0.492</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -3001,19 +3001,19 @@
         <v>12</v>
       </c>
       <c r="C112">
-        <v>0.4453</v>
+        <v>0.4356</v>
       </c>
       <c r="D112">
-        <v>0.5275</v>
+        <v>0.5303</v>
       </c>
       <c r="E112">
-        <v>0.4756999909877777</v>
+        <v>0.4736999869346619</v>
       </c>
       <c r="F112">
         <v>0.3247</v>
       </c>
       <c r="G112">
-        <v>0.4827</v>
+        <v>0.4821</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -3024,19 +3024,19 @@
         <v>13</v>
       </c>
       <c r="C113">
-        <v>0.486</v>
+        <v>0.4773</v>
       </c>
       <c r="D113">
-        <v>0.6058</v>
+        <v>0.6037</v>
       </c>
       <c r="E113">
-        <v>0.5591999888420105</v>
+        <v>0.5242999792098999</v>
       </c>
       <c r="F113">
         <v>0.2503</v>
       </c>
       <c r="G113">
-        <v>0.5407</v>
+        <v>0.532</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -3047,19 +3047,19 @@
         <v>14</v>
       </c>
       <c r="C114">
-        <v>0.4809</v>
+        <v>0.4751</v>
       </c>
       <c r="D114">
-        <v>0.6239</v>
+        <v>0.6187</v>
       </c>
       <c r="E114">
-        <v>0.5619000196456909</v>
+        <v>0.5270000100135803</v>
       </c>
       <c r="F114">
         <v>0.2578</v>
       </c>
       <c r="G114">
-        <v>0.549</v>
+        <v>0.5399</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -3070,19 +3070,19 @@
         <v>15</v>
       </c>
       <c r="C115">
-        <v>0.482</v>
+        <v>0.478</v>
       </c>
       <c r="D115">
-        <v>0.5652</v>
+        <v>0.5602</v>
       </c>
       <c r="E115">
-        <v>0.5307000279426575</v>
+        <v>0.4882000088691711</v>
       </c>
       <c r="F115">
         <v>0.1517</v>
       </c>
       <c r="G115">
-        <v>0.5054</v>
+        <v>0.4949</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -3093,19 +3093,19 @@
         <v>16</v>
       </c>
       <c r="C116">
-        <v>0.4794</v>
+        <v>0.478</v>
       </c>
       <c r="D116">
-        <v>0.4242</v>
+        <v>0.4246</v>
       </c>
       <c r="E116">
-        <v>0.4963000118732452</v>
+        <v>0.4855999946594238</v>
       </c>
       <c r="F116">
         <v>0.3373</v>
       </c>
       <c r="G116">
-        <v>0.4491</v>
+        <v>0.4451</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -3116,19 +3116,19 @@
         <v>17</v>
       </c>
       <c r="C117">
-        <v>0.4757</v>
+        <v>0.473</v>
       </c>
       <c r="D117">
-        <v>0.4738</v>
+        <v>0.482</v>
       </c>
       <c r="E117">
-        <v>0.5228000283241272</v>
+        <v>0.5138999819755554</v>
       </c>
       <c r="F117">
         <v>0.5245</v>
       </c>
       <c r="G117">
-        <v>0.4944</v>
+        <v>0.4948</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -3139,19 +3139,19 @@
         <v>18</v>
       </c>
       <c r="C118">
-        <v>0.4422</v>
+        <v>0.4388</v>
       </c>
       <c r="D118">
-        <v>0.5392</v>
+        <v>0.5451</v>
       </c>
       <c r="E118">
-        <v>0.4652000069618225</v>
+        <v>0.4562999904155731</v>
       </c>
       <c r="F118">
         <v>0.6006</v>
       </c>
       <c r="G118">
-        <v>0.5114</v>
+        <v>0.5135999999999999</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -3162,19 +3162,19 @@
         <v>19</v>
       </c>
       <c r="C119">
-        <v>0.4501</v>
+        <v>0.4443</v>
       </c>
       <c r="D119">
-        <v>0.5117</v>
+        <v>0.5157</v>
       </c>
       <c r="E119">
-        <v>0.4521999955177307</v>
+        <v>0.4433999955654144</v>
       </c>
       <c r="F119">
         <v>0.6657999999999999</v>
       </c>
       <c r="G119">
-        <v>0.5043</v>
+        <v>0.5046</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -3185,19 +3185,19 @@
         <v>20</v>
       </c>
       <c r="C120">
-        <v>0.4413</v>
+        <v>0.4366</v>
       </c>
       <c r="D120">
-        <v>0.5232</v>
+        <v>0.5278</v>
       </c>
       <c r="E120">
-        <v>0.450300008058548</v>
+        <v>0.4408999979496002</v>
       </c>
       <c r="F120">
         <v>0.5966</v>
       </c>
       <c r="G120">
-        <v>0.5003</v>
+        <v>0.5013</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -3208,19 +3208,19 @@
         <v>21</v>
       </c>
       <c r="C121">
-        <v>0.4463</v>
+        <v>0.4335</v>
       </c>
       <c r="D121">
-        <v>0.6042999999999999</v>
+        <v>0.5991</v>
       </c>
       <c r="E121">
-        <v>0.4517999887466431</v>
+        <v>0.4388999938964844</v>
       </c>
       <c r="F121">
         <v>0.5769</v>
       </c>
       <c r="G121">
-        <v>0.5382</v>
+        <v>0.5335</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -3231,19 +3231,19 @@
         <v>10</v>
       </c>
       <c r="C122">
-        <v>0.2194</v>
+        <v>0.2181</v>
       </c>
       <c r="D122">
-        <v>0.3325</v>
+        <v>0.3355</v>
       </c>
       <c r="E122">
-        <v>0.2264000028371811</v>
+        <v>0.2243999987840652</v>
       </c>
       <c r="F122">
         <v>0.1711</v>
       </c>
       <c r="G122">
-        <v>0.2628</v>
+        <v>0.2661</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -3254,19 +3254,19 @@
         <v>11</v>
       </c>
       <c r="C123">
-        <v>0.2198</v>
+        <v>0.2179</v>
       </c>
       <c r="D123">
-        <v>0.3367</v>
+        <v>0.3397</v>
       </c>
       <c r="E123">
-        <v>0.2330999970436096</v>
+        <v>0.2303999960422516</v>
       </c>
       <c r="F123">
         <v>0.0998</v>
       </c>
       <c r="G123">
-        <v>0.2594</v>
+        <v>0.2623</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -3277,19 +3277,19 @@
         <v>12</v>
       </c>
       <c r="C124">
-        <v>0.2158</v>
+        <v>0.2127</v>
       </c>
       <c r="D124">
-        <v>0.3423</v>
+        <v>0.339</v>
       </c>
       <c r="E124">
-        <v>0.2466000020503998</v>
+        <v>0.2446999996900558</v>
       </c>
       <c r="F124">
         <v>0.1129</v>
       </c>
       <c r="G124">
-        <v>0.2649</v>
+        <v>0.2642</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -3300,19 +3300,19 @@
         <v>13</v>
       </c>
       <c r="C125">
-        <v>0.3852</v>
+        <v>0.3829</v>
       </c>
       <c r="D125">
         <v>0.4709</v>
       </c>
       <c r="E125">
-        <v>0.4483000040054321</v>
+        <v>0.4370999932289124</v>
       </c>
       <c r="F125">
         <v>0.125</v>
       </c>
       <c r="G125">
-        <v>0.4147</v>
+        <v>0.4124</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -3323,19 +3323,19 @@
         <v>14</v>
       </c>
       <c r="C126">
-        <v>0.4024</v>
+        <v>0.3974</v>
       </c>
       <c r="D126">
-        <v>0.4776</v>
+        <v>0.4804</v>
       </c>
       <c r="E126">
-        <v>0.4325000047683716</v>
+        <v>0.4318000078201294</v>
       </c>
       <c r="F126">
         <v>0.1275</v>
       </c>
       <c r="G126">
-        <v>0.4198</v>
+        <v>0.4205</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -3346,19 +3346,19 @@
         <v>15</v>
       </c>
       <c r="C127">
-        <v>0.3892</v>
+        <v>0.3827</v>
       </c>
       <c r="D127">
-        <v>0.4372</v>
+        <v>0.4453</v>
       </c>
       <c r="E127">
-        <v>0.4187000095844269</v>
+        <v>0.4189999997615814</v>
       </c>
       <c r="F127">
         <v>0.0892</v>
       </c>
       <c r="G127">
-        <v>0.3907</v>
+        <v>0.3931</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -3369,19 +3369,19 @@
         <v>16</v>
       </c>
       <c r="C128">
-        <v>0.2126</v>
+        <v>0.2148</v>
       </c>
       <c r="D128">
-        <v>0.3478</v>
+        <v>0.3509</v>
       </c>
       <c r="E128">
-        <v>0.240899994969368</v>
+        <v>0.239099994301796</v>
       </c>
       <c r="F128">
         <v>0.0346</v>
       </c>
       <c r="G128">
-        <v>0.258</v>
+        <v>0.2623</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -3392,19 +3392,19 @@
         <v>17</v>
       </c>
       <c r="C129">
-        <v>0.2061</v>
+        <v>0.2066</v>
       </c>
       <c r="D129">
         <v>0.3418</v>
       </c>
       <c r="E129">
-        <v>0.2293999940156937</v>
+        <v>0.229200005531311</v>
       </c>
       <c r="F129">
         <v>0.1278</v>
       </c>
       <c r="G129">
-        <v>0.2599</v>
+        <v>0.2626</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -3415,19 +3415,19 @@
         <v>18</v>
       </c>
       <c r="C130">
-        <v>0.2155</v>
+        <v>0.2142</v>
       </c>
       <c r="D130">
-        <v>0.372</v>
+        <v>0.3748</v>
       </c>
       <c r="E130">
-        <v>0.2178000062704086</v>
+        <v>0.2203000038862228</v>
       </c>
       <c r="F130">
         <v>0.1201</v>
       </c>
       <c r="G130">
-        <v>0.2737</v>
+        <v>0.2788</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -3438,19 +3438,19 @@
         <v>19</v>
       </c>
       <c r="C131">
-        <v>0.2177</v>
+        <v>0.2119</v>
       </c>
       <c r="D131">
-        <v>0.3835</v>
+        <v>0.3863</v>
       </c>
       <c r="E131">
-        <v>0.2270999997854233</v>
+        <v>0.2289000004529953</v>
       </c>
       <c r="F131">
         <v>0.0534</v>
       </c>
       <c r="G131">
-        <v>0.2753</v>
+        <v>0.279</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -3461,19 +3461,19 @@
         <v>20</v>
       </c>
       <c r="C132">
-        <v>0.2127</v>
+        <v>0.2095</v>
       </c>
       <c r="D132">
-        <v>0.3737</v>
+        <v>0.3765</v>
       </c>
       <c r="E132">
-        <v>0.2340999990701675</v>
+        <v>0.2344000041484833</v>
       </c>
       <c r="F132">
         <v>0.0276</v>
       </c>
       <c r="G132">
-        <v>0.2682</v>
+        <v>0.2719</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -3484,19 +3484,19 @@
         <v>21</v>
       </c>
       <c r="C133">
-        <v>0.2316</v>
+        <v>0.2281</v>
       </c>
       <c r="D133">
-        <v>0.3594</v>
+        <v>0.3561</v>
       </c>
       <c r="E133">
-        <v>0.2732000052928925</v>
+        <v>0.2736000120639801</v>
       </c>
       <c r="F133">
         <v>0.0324</v>
       </c>
       <c r="G133">
-        <v>0.2751</v>
+        <v>0.2744</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -3507,19 +3507,19 @@
         <v>10</v>
       </c>
       <c r="C134">
-        <v>0.375</v>
+        <v>0.3799</v>
       </c>
       <c r="D134">
-        <v>0.4681</v>
+        <v>0.4623</v>
       </c>
       <c r="E134">
-        <v>0.4593999981880188</v>
+        <v>0.460999995470047</v>
       </c>
       <c r="F134">
         <v>0.09039999999999999</v>
       </c>
       <c r="G134">
-        <v>0.4095</v>
+        <v>0.4081</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -3530,19 +3530,19 @@
         <v>11</v>
       </c>
       <c r="C135">
-        <v>0.3744</v>
+        <v>0.3756</v>
       </c>
       <c r="D135">
-        <v>0.4193</v>
+        <v>0.4231</v>
       </c>
       <c r="E135">
-        <v>0.4508999884128571</v>
+        <v>0.4541000127792358</v>
       </c>
       <c r="F135">
         <v>0.1404</v>
       </c>
       <c r="G135">
-        <v>0.3894</v>
+        <v>0.391</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -3553,19 +3553,19 @@
         <v>12</v>
       </c>
       <c r="C136">
-        <v>0.3733</v>
+        <v>0.3679</v>
       </c>
       <c r="D136">
-        <v>0.4305</v>
+        <v>0.4343</v>
       </c>
       <c r="E136">
-        <v>0.4706999957561493</v>
+        <v>0.473800003528595</v>
       </c>
       <c r="F136">
         <v>0.1767</v>
       </c>
       <c r="G136">
-        <v>0.4018</v>
+        <v>0.4013</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -3576,19 +3576,19 @@
         <v>13</v>
       </c>
       <c r="C137">
-        <v>0.3471</v>
+        <v>0.3344</v>
       </c>
       <c r="D137">
-        <v>0.4226</v>
+        <v>0.4193</v>
       </c>
       <c r="E137">
-        <v>0.4149999916553497</v>
+        <v>0.4153999984264374</v>
       </c>
       <c r="F137">
         <v>0.1178</v>
       </c>
       <c r="G137">
-        <v>0.3739</v>
+        <v>0.3686</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -3599,19 +3599,19 @@
         <v>14</v>
       </c>
       <c r="C138">
-        <v>0.2472</v>
+        <v>0.2446</v>
       </c>
       <c r="D138">
-        <v>0.4206</v>
+        <v>0.4145</v>
       </c>
       <c r="E138">
-        <v>0.2806000113487244</v>
+        <v>0.2845999896526337</v>
       </c>
       <c r="F138">
         <v>0.1043</v>
       </c>
       <c r="G138">
-        <v>0.3166</v>
+        <v>0.3168</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -3622,19 +3622,19 @@
         <v>15</v>
       </c>
       <c r="C139">
-        <v>0.4117</v>
+        <v>0.4064</v>
       </c>
       <c r="D139">
-        <v>0.5068</v>
+        <v>0.5007</v>
       </c>
       <c r="E139">
-        <v>0.4828999936580658</v>
+        <v>0.4846999943256378</v>
       </c>
       <c r="F139">
         <v>0.1747</v>
       </c>
       <c r="G139">
-        <v>0.4508</v>
+        <v>0.4468</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -3645,19 +3645,19 @@
         <v>16</v>
       </c>
       <c r="C140">
-        <v>0.3152</v>
+        <v>0.3134</v>
       </c>
       <c r="D140">
-        <v>0.4106</v>
+        <v>0.4158</v>
       </c>
       <c r="E140">
-        <v>0.3916999995708466</v>
+        <v>0.3957000076770782</v>
       </c>
       <c r="F140">
         <v>0.2392</v>
       </c>
       <c r="G140">
-        <v>0.3661</v>
+        <v>0.3691</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -3668,19 +3668,19 @@
         <v>17</v>
       </c>
       <c r="C141">
-        <v>0.3223</v>
+        <v>0.3213</v>
       </c>
       <c r="D141">
-        <v>0.4269</v>
+        <v>0.4321</v>
       </c>
       <c r="E141">
-        <v>0.3842000067234039</v>
+        <v>0.3837000131607056</v>
       </c>
       <c r="F141">
         <v>0.2862</v>
       </c>
       <c r="G141">
-        <v>0.3788</v>
+        <v>0.3818</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -3691,19 +3691,19 @@
         <v>18</v>
       </c>
       <c r="C142">
-        <v>0.3215</v>
+        <v>0.3208</v>
       </c>
       <c r="D142">
-        <v>0.3805</v>
+        <v>0.3726</v>
       </c>
       <c r="E142">
-        <v>0.3705999851226807</v>
+        <v>0.3707000017166138</v>
       </c>
       <c r="F142">
         <v>0.2771</v>
       </c>
       <c r="G142">
-        <v>0.3531</v>
+        <v>0.3491</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -3714,19 +3714,19 @@
         <v>19</v>
       </c>
       <c r="C143">
-        <v>0.2146</v>
+        <v>0.2165</v>
       </c>
       <c r="D143">
-        <v>0.329</v>
+        <v>0.326</v>
       </c>
       <c r="E143">
-        <v>0.2442000061273575</v>
+        <v>0.2436999976634979</v>
       </c>
       <c r="F143">
         <v>0.287</v>
       </c>
       <c r="G143">
-        <v>0.2744</v>
+        <v>0.2753</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -3737,10 +3737,10 @@
         <v>20</v>
       </c>
       <c r="C144">
-        <v>0.3865</v>
+        <v>0.3796</v>
       </c>
       <c r="D144">
-        <v>0.4305</v>
+        <v>0.4228</v>
       </c>
       <c r="E144">
         <v>0.4679999947547913</v>
@@ -3749,7 +3749,7 @@
         <v>0.335</v>
       </c>
       <c r="G144">
-        <v>0.42</v>
+        <v>0.413</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -3760,19 +3760,19 @@
         <v>21</v>
       </c>
       <c r="C145">
-        <v>0.384</v>
+        <v>0.3803</v>
       </c>
       <c r="D145">
-        <v>0.4307</v>
+        <v>0.4336</v>
       </c>
       <c r="E145">
-        <v>0.4751999974250793</v>
+        <v>0.4745999872684479</v>
       </c>
       <c r="F145">
         <v>0.2646</v>
       </c>
       <c r="G145">
-        <v>0.4141</v>
+        <v>0.413</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -3783,19 +3783,19 @@
         <v>10</v>
       </c>
       <c r="C146">
-        <v>0.2379</v>
+        <v>0.2355</v>
       </c>
       <c r="D146">
         <v>0.2713</v>
       </c>
       <c r="E146">
-        <v>0.2773999869823456</v>
+        <v>0.2737999856472015</v>
       </c>
       <c r="F146">
         <v>0.1576</v>
       </c>
       <c r="G146">
-        <v>0.2482</v>
+        <v>0.2465</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -3806,7 +3806,7 @@
         <v>11</v>
       </c>
       <c r="C147">
-        <v>0.2293</v>
+        <v>0.2262</v>
       </c>
       <c r="D147">
         <v>0.2698</v>
@@ -3818,7 +3818,7 @@
         <v>0.2462</v>
       </c>
       <c r="G147">
-        <v>0.2406</v>
+        <v>0.2411</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -3829,19 +3829,19 @@
         <v>12</v>
       </c>
       <c r="C148">
-        <v>0.2509</v>
+        <v>0.2475</v>
       </c>
       <c r="D148">
-        <v>0.2894</v>
+        <v>0.2861</v>
       </c>
       <c r="E148">
-        <v>0.2370000034570694</v>
+        <v>0.2281000018119812</v>
       </c>
       <c r="F148">
         <v>0.3455</v>
       </c>
       <c r="G148">
-        <v>0.2701</v>
+        <v>0.2672</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -3852,19 +3852,19 @@
         <v>13</v>
       </c>
       <c r="C149">
-        <v>0.2325</v>
+        <v>0.2303</v>
       </c>
       <c r="D149">
         <v>0.2698</v>
       </c>
       <c r="E149">
-        <v>0.2585999965667725</v>
+        <v>0.2497999966144562</v>
       </c>
       <c r="F149">
         <v>0.2881</v>
       </c>
       <c r="G149">
-        <v>0.2546</v>
+        <v>0.2526</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -3875,19 +3875,19 @@
         <v>14</v>
       </c>
       <c r="C150">
-        <v>0.2285</v>
+        <v>0.2275</v>
       </c>
       <c r="D150">
         <v>0.2655</v>
       </c>
       <c r="E150">
-        <v>0.2565999925136566</v>
+        <v>0.2477000057697296</v>
       </c>
       <c r="F150">
         <v>0.2829</v>
       </c>
       <c r="G150">
-        <v>0.2505</v>
+        <v>0.2488</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -3898,19 +3898,19 @@
         <v>15</v>
       </c>
       <c r="C151">
-        <v>0.2311</v>
+        <v>0.2307</v>
       </c>
       <c r="D151">
         <v>0.2692</v>
       </c>
       <c r="E151">
-        <v>0.2626000046730042</v>
+        <v>0.2538000047206879</v>
       </c>
       <c r="F151">
         <v>0.2978</v>
       </c>
       <c r="G151">
-        <v>0.2556</v>
+        <v>0.254</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -3921,19 +3921,19 @@
         <v>16</v>
       </c>
       <c r="C152">
-        <v>0.2292</v>
+        <v>0.2278</v>
       </c>
       <c r="D152">
         <v>0.279</v>
       </c>
       <c r="E152">
-        <v>0.274399995803833</v>
+        <v>0.265500009059906</v>
       </c>
       <c r="F152">
         <v>0.3022</v>
       </c>
       <c r="G152">
-        <v>0.2624</v>
+        <v>0.2605</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -3944,19 +3944,19 @@
         <v>17</v>
       </c>
       <c r="C153">
-        <v>0.3632</v>
+        <v>0.3689</v>
       </c>
       <c r="D153">
-        <v>0.3752</v>
+        <v>0.3936</v>
       </c>
       <c r="E153">
-        <v>0.4945000112056732</v>
+        <v>0.4828000068664551</v>
       </c>
       <c r="F153">
         <v>0.4091</v>
       </c>
       <c r="G153">
-        <v>0.3998</v>
+        <v>0.4052</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -3967,19 +3967,19 @@
         <v>18</v>
       </c>
       <c r="C154">
-        <v>0.3679</v>
+        <v>0.3739</v>
       </c>
       <c r="D154">
-        <v>0.3912</v>
+        <v>0.4096</v>
       </c>
       <c r="E154">
-        <v>0.4941999912261963</v>
+        <v>0.4824999868869781</v>
       </c>
       <c r="F154">
         <v>0.4023</v>
       </c>
       <c r="G154">
-        <v>0.4079</v>
+        <v>0.4138</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -3993,16 +3993,16 @@
         <v>0.3674</v>
       </c>
       <c r="D155">
-        <v>0.3655</v>
+        <v>0.3666</v>
       </c>
       <c r="E155">
-        <v>0.4887999892234802</v>
+        <v>0.488400012254715</v>
       </c>
       <c r="F155">
         <v>0.3729</v>
       </c>
       <c r="G155">
-        <v>0.3918</v>
+        <v>0.3889</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -4013,10 +4013,10 @@
         <v>20</v>
       </c>
       <c r="C156">
-        <v>0.2428</v>
+        <v>0.2412</v>
       </c>
       <c r="D156">
-        <v>0.2898</v>
+        <v>0.2844</v>
       </c>
       <c r="E156">
         <v>0.2382999956607819</v>
@@ -4025,7 +4025,7 @@
         <v>0.3478</v>
       </c>
       <c r="G156">
-        <v>0.2684</v>
+        <v>0.2666</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -4036,7 +4036,7 @@
         <v>21</v>
       </c>
       <c r="C157">
-        <v>0.2726</v>
+        <v>0.2721</v>
       </c>
       <c r="D157">
         <v>0.2906</v>
@@ -4048,7 +4048,7 @@
         <v>0.2024</v>
       </c>
       <c r="G157">
-        <v>0.2664</v>
+        <v>0.2671</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -4062,7 +4062,7 @@
         <v>0.3039</v>
       </c>
       <c r="D158">
-        <v>0.299</v>
+        <v>0.2947</v>
       </c>
       <c r="E158">
         <v>0.3077000081539154</v>
@@ -4071,7 +4071,7 @@
         <v>0.4255</v>
       </c>
       <c r="G158">
-        <v>0.3113</v>
+        <v>0.3089</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -4082,10 +4082,10 @@
         <v>11</v>
       </c>
       <c r="C159">
-        <v>0.3043</v>
+        <v>0.3049</v>
       </c>
       <c r="D159">
-        <v>0.2939</v>
+        <v>0.2895</v>
       </c>
       <c r="E159">
         <v>0.3075999915599823</v>
@@ -4094,7 +4094,7 @@
         <v>0.437</v>
       </c>
       <c r="G159">
-        <v>0.31</v>
+        <v>0.3077</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -4105,19 +4105,19 @@
         <v>12</v>
       </c>
       <c r="C160">
-        <v>0.3007</v>
+        <v>0.3009</v>
       </c>
       <c r="D160">
-        <v>0.2948</v>
+        <v>0.3025</v>
       </c>
       <c r="E160">
-        <v>0.323500007390976</v>
+        <v>0.3145999908447266</v>
       </c>
       <c r="F160">
         <v>0.4339</v>
       </c>
       <c r="G160">
-        <v>0.3124</v>
+        <v>0.3139</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -4128,19 +4128,19 @@
         <v>13</v>
       </c>
       <c r="C161">
-        <v>0.2609</v>
+        <v>0.2589</v>
       </c>
       <c r="D161">
-        <v>0.3059</v>
+        <v>0.3027</v>
       </c>
       <c r="E161">
-        <v>0.2504999935626984</v>
+        <v>0.239999994635582</v>
       </c>
       <c r="F161">
         <v>0.3918</v>
       </c>
       <c r="G161">
-        <v>0.2878</v>
+        <v>0.2851</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -4151,19 +4151,19 @@
         <v>14</v>
       </c>
       <c r="C162">
-        <v>0.2562</v>
+        <v>0.2536</v>
       </c>
       <c r="D162">
-        <v>0.3091</v>
+        <v>0.3058</v>
       </c>
       <c r="E162">
-        <v>0.2651000022888184</v>
+        <v>0.2635000050067902</v>
       </c>
       <c r="F162">
         <v>0.2932</v>
       </c>
       <c r="G162">
-        <v>0.2815</v>
+        <v>0.2798</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -4174,19 +4174,19 @@
         <v>15</v>
       </c>
       <c r="C163">
-        <v>0.2525</v>
+        <v>0.2492</v>
       </c>
       <c r="D163">
-        <v>0.3111</v>
+        <v>0.3079</v>
       </c>
       <c r="E163">
-        <v>0.2709000110626221</v>
+        <v>0.2693000137805939</v>
       </c>
       <c r="F163">
         <v>0.2981</v>
       </c>
       <c r="G163">
-        <v>0.2831</v>
+        <v>0.2811</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -4197,19 +4197,19 @@
         <v>16</v>
       </c>
       <c r="C164">
-        <v>0.2568</v>
+        <v>0.2548</v>
       </c>
       <c r="D164">
-        <v>0.3083</v>
+        <v>0.305</v>
       </c>
       <c r="E164">
-        <v>0.2454999983310699</v>
+        <v>0.2439000010490417</v>
       </c>
       <c r="F164">
         <v>0.4196</v>
       </c>
       <c r="G164">
-        <v>0.2893</v>
+        <v>0.2884</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -4220,10 +4220,10 @@
         <v>17</v>
       </c>
       <c r="C165">
-        <v>0.3061</v>
+        <v>0.3058</v>
       </c>
       <c r="D165">
-        <v>0.2931</v>
+        <v>0.2941</v>
       </c>
       <c r="E165">
         <v>0.3070000112056732</v>
@@ -4232,7 +4232,7 @@
         <v>0.5119</v>
       </c>
       <c r="G165">
-        <v>0.3172</v>
+        <v>0.3173</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -4243,10 +4243,10 @@
         <v>18</v>
       </c>
       <c r="C166">
-        <v>0.3127</v>
+        <v>0.313</v>
       </c>
       <c r="D166">
-        <v>0.2921</v>
+        <v>0.2931</v>
       </c>
       <c r="E166">
         <v>0.3023000061511993</v>
@@ -4255,7 +4255,7 @@
         <v>0.5478</v>
       </c>
       <c r="G166">
-        <v>0.321</v>
+        <v>0.3214</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -4266,10 +4266,10 @@
         <v>19</v>
       </c>
       <c r="C167">
-        <v>0.3556</v>
+        <v>0.3566</v>
       </c>
       <c r="D167">
-        <v>0.3222</v>
+        <v>0.3245</v>
       </c>
       <c r="E167">
         <v>0.3519000113010406</v>
@@ -4278,7 +4278,7 @@
         <v>0.5396</v>
       </c>
       <c r="G167">
-        <v>0.3564</v>
+        <v>0.3572</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -4289,19 +4289,19 @@
         <v>20</v>
       </c>
       <c r="C168">
-        <v>0.3649</v>
+        <v>0.3655</v>
       </c>
       <c r="D168">
-        <v>0.3362</v>
+        <v>0.3439</v>
       </c>
       <c r="E168">
-        <v>0.387499988079071</v>
+        <v>0.4034000039100647</v>
       </c>
       <c r="F168">
         <v>0.5723</v>
       </c>
       <c r="G168">
-        <v>0.3759</v>
+        <v>0.3813</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -4312,10 +4312,10 @@
         <v>21</v>
       </c>
       <c r="C169">
-        <v>0.3482</v>
+        <v>0.3466</v>
       </c>
       <c r="D169">
-        <v>0.3302</v>
+        <v>0.3248</v>
       </c>
       <c r="E169">
         <v>0.3937999904155731</v>
@@ -4324,7 +4324,7 @@
         <v>0.5106000000000001</v>
       </c>
       <c r="G169">
-        <v>0.3638</v>
+        <v>0.359</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -4335,10 +4335,10 @@
         <v>10</v>
       </c>
       <c r="C170">
-        <v>0.2684</v>
+        <v>0.2672</v>
       </c>
       <c r="D170">
-        <v>0.2903</v>
+        <v>0.2899</v>
       </c>
       <c r="E170">
         <v>0.2687999904155731</v>
@@ -4347,7 +4347,7 @@
         <v>0.2104</v>
       </c>
       <c r="G170">
-        <v>0.269</v>
+        <v>0.2689</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -4358,10 +4358,10 @@
         <v>11</v>
       </c>
       <c r="C171">
-        <v>0.2825</v>
+        <v>0.283</v>
       </c>
       <c r="D171">
-        <v>0.2957</v>
+        <v>0.2953</v>
       </c>
       <c r="E171">
         <v>0.3140000104904175</v>
@@ -4370,7 +4370,7 @@
         <v>0.1969</v>
       </c>
       <c r="G171">
-        <v>0.2833</v>
+        <v>0.2826</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -4381,19 +4381,19 @@
         <v>12</v>
       </c>
       <c r="C172">
-        <v>0.2623</v>
+        <v>0.2612</v>
       </c>
       <c r="D172">
-        <v>0.2901</v>
+        <v>0.2897</v>
       </c>
       <c r="E172">
-        <v>0.2712999880313873</v>
+        <v>0.2723000049591064</v>
       </c>
       <c r="F172">
         <v>0.2103</v>
       </c>
       <c r="G172">
-        <v>0.2676</v>
+        <v>0.2677</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -4404,19 +4404,19 @@
         <v>13</v>
       </c>
       <c r="C173">
-        <v>0.281</v>
+        <v>0.2808</v>
       </c>
       <c r="D173">
-        <v>0.294</v>
+        <v>0.2907</v>
       </c>
       <c r="E173">
-        <v>0.3107999861240387</v>
+        <v>0.3030000030994415</v>
       </c>
       <c r="F173">
         <v>0.2038</v>
       </c>
       <c r="G173">
-        <v>0.2821</v>
+        <v>0.2784</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -4427,19 +4427,19 @@
         <v>14</v>
       </c>
       <c r="C174">
-        <v>0.2698</v>
+        <v>0.2675</v>
       </c>
       <c r="D174">
-        <v>0.3018</v>
+        <v>0.3165</v>
       </c>
       <c r="E174">
-        <v>0.2648000121116638</v>
+        <v>0.253600001335144</v>
       </c>
       <c r="F174">
         <v>0.2968</v>
       </c>
       <c r="G174">
-        <v>0.2822</v>
+        <v>0.2877</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -4450,19 +4450,19 @@
         <v>15</v>
       </c>
       <c r="C175">
-        <v>0.3642</v>
+        <v>0.3662</v>
       </c>
       <c r="D175">
-        <v>0.3039</v>
+        <v>0.306</v>
       </c>
       <c r="E175">
-        <v>0.4162000119686127</v>
+        <v>0.4074000120162964</v>
       </c>
       <c r="F175">
         <v>0.3869</v>
       </c>
       <c r="G175">
-        <v>0.3487</v>
+        <v>0.3458</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -4473,19 +4473,19 @@
         <v>16</v>
       </c>
       <c r="C176">
-        <v>0.3613</v>
+        <v>0.3655</v>
       </c>
       <c r="D176">
-        <v>0.3345</v>
+        <v>0.3459</v>
       </c>
       <c r="E176">
-        <v>0.4025000035762787</v>
+        <v>0.3912999927997589</v>
       </c>
       <c r="F176">
         <v>0.396</v>
       </c>
       <c r="G176">
-        <v>0.3604</v>
+        <v>0.3634</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -4496,19 +4496,19 @@
         <v>17</v>
       </c>
       <c r="C177">
-        <v>0.3768</v>
+        <v>0.3883</v>
       </c>
       <c r="D177">
-        <v>0.3636</v>
+        <v>0.3716</v>
       </c>
       <c r="E177">
-        <v>0.4027000069618225</v>
+        <v>0.3914999961853027</v>
       </c>
       <c r="F177">
         <v>0.4383</v>
       </c>
       <c r="G177">
-        <v>0.3824</v>
+        <v>0.3867</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -4519,7 +4519,7 @@
         <v>18</v>
       </c>
       <c r="C178">
-        <v>0.3637</v>
+        <v>0.3683</v>
       </c>
       <c r="D178">
         <v>0.3518</v>
@@ -4531,7 +4531,7 @@
         <v>0.3393</v>
       </c>
       <c r="G178">
-        <v>0.3666</v>
+        <v>0.3661</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -4542,10 +4542,10 @@
         <v>19</v>
       </c>
       <c r="C179">
-        <v>0.342</v>
+        <v>0.3488</v>
       </c>
       <c r="D179">
-        <v>0.3391</v>
+        <v>0.3445</v>
       </c>
       <c r="E179">
         <v>0.3899999856948853</v>
@@ -4554,7 +4554,7 @@
         <v>0.1096</v>
       </c>
       <c r="G179">
-        <v>0.3275</v>
+        <v>0.3305</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -4565,10 +4565,10 @@
         <v>20</v>
       </c>
       <c r="C180">
-        <v>0.3025</v>
+        <v>0.3078</v>
       </c>
       <c r="D180">
-        <v>0.295</v>
+        <v>0.3004</v>
       </c>
       <c r="E180">
         <v>0.3176000118255615</v>
@@ -4577,7 +4577,7 @@
         <v>0.0559</v>
       </c>
       <c r="G180">
-        <v>0.2759</v>
+        <v>0.2793</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -4588,7 +4588,7 @@
         <v>21</v>
       </c>
       <c r="C181">
-        <v>0.3076</v>
+        <v>0.3074</v>
       </c>
       <c r="D181">
         <v>0.2763</v>
@@ -4600,7 +4600,7 @@
         <v>0.1177</v>
       </c>
       <c r="G181">
-        <v>0.2727</v>
+        <v>0.2717</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -4611,19 +4611,19 @@
         <v>10</v>
       </c>
       <c r="C182">
-        <v>0.2714</v>
+        <v>0.2728</v>
       </c>
       <c r="D182">
         <v>0.2682</v>
       </c>
       <c r="E182">
-        <v>0.2612999975681305</v>
+        <v>0.2700000107288361</v>
       </c>
       <c r="F182">
         <v>0.1179</v>
       </c>
       <c r="G182">
-        <v>0.2491</v>
+        <v>0.2511</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -4634,19 +4634,19 @@
         <v>11</v>
       </c>
       <c r="C183">
-        <v>0.2766</v>
+        <v>0.2778</v>
       </c>
       <c r="D183">
         <v>0.2653</v>
       </c>
       <c r="E183">
-        <v>0.2628999948501587</v>
+        <v>0.2716000080108643</v>
       </c>
       <c r="F183">
         <v>0.1288</v>
       </c>
       <c r="G183">
-        <v>0.2506</v>
+        <v>0.2524</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -4657,19 +4657,19 @@
         <v>12</v>
       </c>
       <c r="C184">
-        <v>0.2776</v>
+        <v>0.279</v>
       </c>
       <c r="D184">
         <v>0.2681</v>
       </c>
       <c r="E184">
-        <v>0.2653999924659729</v>
+        <v>0.2739999890327454</v>
       </c>
       <c r="F184">
         <v>0.138</v>
       </c>
       <c r="G184">
-        <v>0.2536</v>
+        <v>0.2554</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -4680,7 +4680,7 @@
         <v>13</v>
       </c>
       <c r="C185">
-        <v>0.2726</v>
+        <v>0.2715</v>
       </c>
       <c r="D185">
         <v>0.2557</v>
@@ -4692,7 +4692,7 @@
         <v>0</v>
       </c>
       <c r="G185">
-        <v>0.2305</v>
+        <v>0.2299</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -4703,7 +4703,7 @@
         <v>14</v>
       </c>
       <c r="C186">
-        <v>0.2718</v>
+        <v>0.2708</v>
       </c>
       <c r="D186">
         <v>0.2616</v>
@@ -4715,7 +4715,7 @@
         <v>0.0285</v>
       </c>
       <c r="G186">
-        <v>0.2371</v>
+        <v>0.2368</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -4726,19 +4726,19 @@
         <v>15</v>
       </c>
       <c r="C187">
-        <v>0.3734</v>
+        <v>0.3753</v>
       </c>
       <c r="D187">
         <v>0.301</v>
       </c>
       <c r="E187">
-        <v>0.4498000144958496</v>
+        <v>0.4194000065326691</v>
       </c>
       <c r="F187">
         <v>0.2756</v>
       </c>
       <c r="G187">
-        <v>0.3461</v>
+        <v>0.3374</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -4749,19 +4749,19 @@
         <v>16</v>
       </c>
       <c r="C188">
-        <v>0.3621</v>
+        <v>0.3652</v>
       </c>
       <c r="D188">
-        <v>0.3393</v>
+        <v>0.3392</v>
       </c>
       <c r="E188">
-        <v>0.4275999963283539</v>
+        <v>0.4264000058174133</v>
       </c>
       <c r="F188">
         <v>0.2215</v>
       </c>
       <c r="G188">
-        <v>0.3513</v>
+        <v>0.3495</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -4772,19 +4772,19 @@
         <v>17</v>
       </c>
       <c r="C189">
-        <v>0.535</v>
+        <v>0.5332</v>
       </c>
       <c r="D189">
-        <v>0.5283</v>
+        <v>0.5127</v>
       </c>
       <c r="E189">
-        <v>0.4715999960899353</v>
+        <v>0.4688000082969666</v>
       </c>
       <c r="F189">
         <v>0.288</v>
       </c>
       <c r="G189">
-        <v>0.504</v>
+        <v>0.4967</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -4795,19 +4795,19 @@
         <v>18</v>
       </c>
       <c r="C190">
-        <v>0.3686</v>
+        <v>0.3737</v>
       </c>
       <c r="D190">
         <v>0.3498</v>
       </c>
       <c r="E190">
-        <v>0.4359999895095825</v>
+        <v>0.434799998998642</v>
       </c>
       <c r="F190">
         <v>0.0017</v>
       </c>
       <c r="G190">
-        <v>0.3389</v>
+        <v>0.3376</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -4818,19 +4818,19 @@
         <v>19</v>
       </c>
       <c r="C191">
-        <v>0.3192</v>
+        <v>0.3194</v>
       </c>
       <c r="D191">
         <v>0.3445</v>
       </c>
       <c r="E191">
-        <v>0.3806999921798706</v>
+        <v>0.3792999982833862</v>
       </c>
       <c r="F191">
         <v>0</v>
       </c>
       <c r="G191">
-        <v>0.3026</v>
+        <v>0.3011</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -4841,19 +4841,19 @@
         <v>20</v>
       </c>
       <c r="C192">
-        <v>0.319</v>
+        <v>0.3206</v>
       </c>
       <c r="D192">
         <v>0.2869</v>
       </c>
       <c r="E192">
-        <v>0.3348999917507172</v>
+        <v>0.3368000090122223</v>
       </c>
       <c r="F192">
         <v>0</v>
       </c>
       <c r="G192">
-        <v>0.2609</v>
+        <v>0.2602</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -4864,19 +4864,19 @@
         <v>21</v>
       </c>
       <c r="C193">
-        <v>0.3154</v>
+        <v>0.3138</v>
       </c>
       <c r="D193">
         <v>0.2875</v>
       </c>
       <c r="E193">
-        <v>0.3325999975204468</v>
+        <v>0.3345000147819519</v>
       </c>
       <c r="F193">
         <v>0</v>
       </c>
       <c r="G193">
-        <v>0.267</v>
+        <v>0.2655</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -4887,13 +4887,13 @@
         <v>10</v>
       </c>
       <c r="C194">
-        <v>0.3447</v>
+        <v>0.3481</v>
       </c>
       <c r="D194">
         <v>0.3332</v>
       </c>
       <c r="E194">
-        <v>0.3725000023841858</v>
+        <v>0.3743000030517578</v>
       </c>
       <c r="F194">
         <v>0.0086</v>
@@ -4910,7 +4910,7 @@
         <v>11</v>
       </c>
       <c r="C195">
-        <v>0.3352</v>
+        <v>0.3339</v>
       </c>
       <c r="D195">
         <v>0.3251</v>
@@ -4922,7 +4922,7 @@
         <v>0.022</v>
       </c>
       <c r="G195">
-        <v>0.3051</v>
+        <v>0.3036</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -4933,19 +4933,19 @@
         <v>12</v>
       </c>
       <c r="C196">
-        <v>0.3367</v>
+        <v>0.3368</v>
       </c>
       <c r="D196">
         <v>0.3153</v>
       </c>
       <c r="E196">
-        <v>0.3265999853610992</v>
+        <v>0.3332000076770782</v>
       </c>
       <c r="F196">
         <v>0.0482</v>
       </c>
       <c r="G196">
-        <v>0.2962</v>
+        <v>0.2969</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -4956,19 +4956,19 @@
         <v>13</v>
       </c>
       <c r="C197">
-        <v>0.3419</v>
+        <v>0.3412</v>
       </c>
       <c r="D197">
-        <v>0.3089</v>
+        <v>0.3003</v>
       </c>
       <c r="E197">
-        <v>0.3962999880313873</v>
+        <v>0.4149999916553497</v>
       </c>
       <c r="F197">
         <v>0.0481</v>
       </c>
       <c r="G197">
-        <v>0.3086</v>
+        <v>0.3049</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -4979,19 +4979,19 @@
         <v>14</v>
       </c>
       <c r="C198">
-        <v>0.3276</v>
+        <v>0.3332</v>
       </c>
       <c r="D198">
-        <v>0.3096</v>
+        <v>0.3009</v>
       </c>
       <c r="E198">
-        <v>0.3801000118255615</v>
+        <v>0.3711999952793121</v>
       </c>
       <c r="F198">
         <v>0.0101</v>
       </c>
       <c r="G198">
-        <v>0.298</v>
+        <v>0.2918</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -5002,19 +5002,19 @@
         <v>15</v>
       </c>
       <c r="C199">
-        <v>0.4878</v>
+        <v>0.4849</v>
       </c>
       <c r="D199">
-        <v>0.5592</v>
+        <v>0.5438</v>
       </c>
       <c r="E199">
-        <v>0.5504999756813049</v>
+        <v>0.5412999987602234</v>
       </c>
       <c r="F199">
         <v>0.1121</v>
       </c>
       <c r="G199">
-        <v>0.5044999999999999</v>
+        <v>0.4942</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -5025,19 +5025,19 @@
         <v>16</v>
       </c>
       <c r="C200">
-        <v>0.6667999999999999</v>
+        <v>0.6787</v>
       </c>
       <c r="D200">
-        <v>0.5203</v>
+        <v>0.484</v>
       </c>
       <c r="E200">
-        <v>0.4413999915122986</v>
+        <v>0.4420999884605408</v>
       </c>
       <c r="F200">
         <v>0.1808</v>
       </c>
       <c r="G200">
-        <v>0.5211</v>
+        <v>0.509</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -5048,19 +5048,19 @@
         <v>17</v>
       </c>
       <c r="C201">
-        <v>0.6671</v>
+        <v>0.6781</v>
       </c>
       <c r="D201">
-        <v>0.5542</v>
+        <v>0.518</v>
       </c>
       <c r="E201">
-        <v>0.4954999983310699</v>
+        <v>0.4979000091552734</v>
       </c>
       <c r="F201">
         <v>0.1709</v>
       </c>
       <c r="G201">
-        <v>0.5471</v>
+        <v>0.5344</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -5071,19 +5071,19 @@
         <v>18</v>
       </c>
       <c r="C202">
-        <v>0.3719</v>
+        <v>0.3629</v>
       </c>
       <c r="D202">
         <v>0.3824</v>
       </c>
       <c r="E202">
-        <v>0.4341999888420105</v>
+        <v>0.4325999915599823</v>
       </c>
       <c r="F202">
         <v>0.06909999999999999</v>
       </c>
       <c r="G202">
-        <v>0.3613</v>
+        <v>0.3568</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -5094,19 +5094,19 @@
         <v>19</v>
       </c>
       <c r="C203">
-        <v>0.3491</v>
+        <v>0.3426</v>
       </c>
       <c r="D203">
         <v>0.3914</v>
       </c>
       <c r="E203">
-        <v>0.3930000066757202</v>
+        <v>0.3948000073432922</v>
       </c>
       <c r="F203">
         <v>0.0504</v>
       </c>
       <c r="G203">
-        <v>0.349</v>
+        <v>0.3471</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -5117,7 +5117,7 @@
         <v>20</v>
       </c>
       <c r="C204">
-        <v>0.2951</v>
+        <v>0.3029</v>
       </c>
       <c r="D204">
         <v>0.3161</v>
@@ -5129,7 +5129,7 @@
         <v>0.0268</v>
       </c>
       <c r="G204">
-        <v>0.2786</v>
+        <v>0.2808</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -5140,7 +5140,7 @@
         <v>21</v>
       </c>
       <c r="C205">
-        <v>0.2961</v>
+        <v>0.3014</v>
       </c>
       <c r="D205">
         <v>0.3169</v>
@@ -5152,7 +5152,7 @@
         <v>0.0159</v>
       </c>
       <c r="G205">
-        <v>0.2792</v>
+        <v>0.2806</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -5163,10 +5163,10 @@
         <v>10</v>
       </c>
       <c r="C206">
-        <v>0.2489</v>
+        <v>0.2506</v>
       </c>
       <c r="D206">
-        <v>0.3124</v>
+        <v>0.3108</v>
       </c>
       <c r="E206">
         <v>0.3655999898910522</v>
@@ -5175,7 +5175,7 @@
         <v>0.1251</v>
       </c>
       <c r="G206">
-        <v>0.2852</v>
+        <v>0.2832</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -5186,10 +5186,10 @@
         <v>11</v>
       </c>
       <c r="C207">
-        <v>0.2484</v>
+        <v>0.2517</v>
       </c>
       <c r="D207">
-        <v>0.3062</v>
+        <v>0.3046</v>
       </c>
       <c r="E207">
         <v>0.3407999873161316</v>
@@ -5198,7 +5198,7 @@
         <v>0.1438</v>
       </c>
       <c r="G207">
-        <v>0.2789</v>
+        <v>0.2779</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -5209,10 +5209,10 @@
         <v>12</v>
       </c>
       <c r="C208">
-        <v>0.2401</v>
+        <v>0.244</v>
       </c>
       <c r="D208">
-        <v>0.298</v>
+        <v>0.2964</v>
       </c>
       <c r="E208">
         <v>0.3580000102519989</v>
@@ -5221,7 +5221,7 @@
         <v>0.1427</v>
       </c>
       <c r="G208">
-        <v>0.2761</v>
+        <v>0.2746</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -5232,19 +5232,19 @@
         <v>13</v>
       </c>
       <c r="C209">
-        <v>0.2575</v>
+        <v>0.2684</v>
       </c>
       <c r="D209">
-        <v>0.265</v>
+        <v>0.2645</v>
       </c>
       <c r="E209">
-        <v>0.3246000111103058</v>
+        <v>0.3282999992370605</v>
       </c>
       <c r="F209">
         <v>0.151</v>
       </c>
       <c r="G209">
-        <v>0.2596</v>
+        <v>0.2613</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -5255,10 +5255,10 @@
         <v>14</v>
       </c>
       <c r="C210">
-        <v>0.2698</v>
+        <v>0.2836</v>
       </c>
       <c r="D210">
-        <v>0.2875</v>
+        <v>0.2876</v>
       </c>
       <c r="E210">
         <v>0.3312000036239624</v>
@@ -5267,7 +5267,7 @@
         <v>0.0597</v>
       </c>
       <c r="G210">
-        <v>0.2663</v>
+        <v>0.2689</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -5278,19 +5278,19 @@
         <v>15</v>
       </c>
       <c r="C211">
-        <v>0.2616</v>
+        <v>0.2658</v>
       </c>
       <c r="D211">
-        <v>0.3061</v>
+        <v>0.3203</v>
       </c>
       <c r="E211">
-        <v>0.3355000019073486</v>
+        <v>0.3337000012397766</v>
       </c>
       <c r="F211">
         <v>0.097</v>
       </c>
       <c r="G211">
-        <v>0.2771</v>
+        <v>0.284</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -5301,10 +5301,10 @@
         <v>16</v>
       </c>
       <c r="C212">
-        <v>0.2513</v>
+        <v>0.2505</v>
       </c>
       <c r="D212">
-        <v>0.2839</v>
+        <v>0.2976</v>
       </c>
       <c r="E212">
         <v>0.2894999980926514</v>
@@ -5313,7 +5313,7 @@
         <v>0.0648</v>
       </c>
       <c r="G212">
-        <v>0.2515</v>
+        <v>0.2577</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -5324,19 +5324,19 @@
         <v>17</v>
       </c>
       <c r="C213">
-        <v>0.2433</v>
+        <v>0.2452</v>
       </c>
       <c r="D213">
-        <v>0.3141</v>
+        <v>0.3228</v>
       </c>
       <c r="E213">
-        <v>0.3109999895095825</v>
+        <v>0.3118000030517578</v>
       </c>
       <c r="F213">
         <v>0.0444</v>
       </c>
       <c r="G213">
-        <v>0.2658</v>
+        <v>0.2706</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -5347,19 +5347,19 @@
         <v>18</v>
       </c>
       <c r="C214">
-        <v>0.2293</v>
+        <v>0.2307</v>
       </c>
       <c r="D214">
-        <v>0.289</v>
+        <v>0.2977</v>
       </c>
       <c r="E214">
-        <v>0.3190000057220459</v>
+        <v>0.3197999894618988</v>
       </c>
       <c r="F214">
         <v>0.2106</v>
       </c>
       <c r="G214">
-        <v>0.2675</v>
+        <v>0.2713</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -5370,19 +5370,19 @@
         <v>19</v>
       </c>
       <c r="C215">
-        <v>0.674</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="D215">
-        <v>0.617</v>
+        <v>0.5681</v>
       </c>
       <c r="E215">
-        <v>0.5353000164031982</v>
+        <v>0.5386999845504761</v>
       </c>
       <c r="F215">
         <v>0.3593</v>
       </c>
       <c r="G215">
-        <v>0.6045</v>
+        <v>0.5873</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -5393,19 +5393,19 @@
         <v>20</v>
       </c>
       <c r="C216">
-        <v>0.2596</v>
+        <v>0.2585</v>
       </c>
       <c r="D216">
-        <v>0.2842</v>
+        <v>0.2827</v>
       </c>
       <c r="E216">
-        <v>0.3000999987125397</v>
+        <v>0.2942000031471252</v>
       </c>
       <c r="F216">
         <v>0.2518</v>
       </c>
       <c r="G216">
-        <v>0.2739</v>
+        <v>0.2712</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -5416,19 +5416,19 @@
         <v>21</v>
       </c>
       <c r="C217">
-        <v>0.2106</v>
+        <v>0.2072</v>
       </c>
       <c r="D217">
-        <v>0.2971</v>
+        <v>0.2984</v>
       </c>
       <c r="E217">
-        <v>0.2485000044107437</v>
+        <v>0.2470999956130981</v>
       </c>
       <c r="F217">
         <v>0.2842</v>
       </c>
       <c r="G217">
-        <v>0.2588</v>
+        <v>0.2593</v>
       </c>
     </row>
   </sheetData>
